--- a/data/base-text-sop.xlsx
+++ b/data/base-text-sop.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-protocols/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB4B671C-FDB1-D14C-8628-0BA3CA8DB272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACFAA29F-15CA-5D4A-96D1-FE44D0CFA79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2680" yWindow="600" windowWidth="25360" windowHeight="16960" xr2:uid="{CCA2DD50-73A2-AB48-A73E-30174A4C4548}"/>
+    <workbookView xWindow="60" yWindow="600" windowWidth="30660" windowHeight="16980" xr2:uid="{CCA2DD50-73A2-AB48-A73E-30174A4C4548}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sweetpotato" sheetId="1" r:id="rId1"/>
+    <sheet name="text" sheetId="1" r:id="rId1"/>
+    <sheet name="other_resources" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_Toc219906839" localSheetId="0">Sweetpotato!$A$6</definedName>
-    <definedName name="_Toc219906845" localSheetId="0">Sweetpotato!#REF!</definedName>
-    <definedName name="_Toc219906846" localSheetId="0">Sweetpotato!$A$13</definedName>
-    <definedName name="_Toc219906847" localSheetId="0">Sweetpotato!#REF!</definedName>
-    <definedName name="_Toc219906848" localSheetId="0">Sweetpotato!#REF!</definedName>
-    <definedName name="_Toc219906849" localSheetId="0">Sweetpotato!#REF!</definedName>
-    <definedName name="_Toc219906850" localSheetId="0">Sweetpotato!#REF!</definedName>
+    <definedName name="_Toc219906839" localSheetId="0">text!$A$8</definedName>
+    <definedName name="_Toc219906845" localSheetId="0">text!#REF!</definedName>
+    <definedName name="_Toc219906846" localSheetId="0">text!#REF!</definedName>
+    <definedName name="_Toc219906847" localSheetId="0">text!#REF!</definedName>
+    <definedName name="_Toc219906848" localSheetId="0">text!#REF!</definedName>
+    <definedName name="_Toc219906849" localSheetId="0">text!#REF!</definedName>
+    <definedName name="_Toc219906850" localSheetId="0">text!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="62">
   <si>
     <t>en</t>
   </si>
@@ -80,92 +81,167 @@
     <t>Introdução</t>
   </si>
   <si>
-    <t>In ClimMob we prepared a tool to help you calculate the number of seeds needed for each package. First, you must define the plot size and plant density. Check the tool here &lt;Trial dimensions – ClimMob Documentation&gt;</t>
-  </si>
-  <si>
     <t>Informed consent</t>
   </si>
   <si>
-    <t>This informed consent form provides a standardised framework to ensure that all participants are adequately informed before taking part in tricot trials and associated surveys. It explains the purpose of the data collection, the types of information that will be collected, and how these data may be used, including for research and publication.</t>
-  </si>
-  <si>
-    <t>Participation is entirely voluntary. Participants may decline to answer any question or withdraw from the study at any time, without any negative consequences. Consent is obtained before data collection to ensure transparency, ethical research practice, and respect for participants’ rights. Providing informed consent is a prerequisite for inclusion in all subsequent trial and survey activities.</t>
-  </si>
-  <si>
-    <t>This document can be completed manually or downloaded directly from the Climmob “Downloads” section.</t>
-  </si>
-  <si>
-    <t>Table 1 outlines the data collection moments and traits to be collected during the tricot trial. Data collection is organized around the main stages of the trial cycle: participant registration and baseline characterization, trial establishment, early crop development, harvest, and post-harvest assessment.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data collection moments and traits to be collected </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Table 1. Data collection moments and traits </t>
-  </si>
-  <si>
-    <t>Table 2 contains the household and trial characterisation questions that will be asked to complement the core tricot questions. These questions provide contextual information that is necessary to interpret the results of the sweet potato tricot trial across different participant profiles, production systems, and local environments.</t>
-  </si>
-  <si>
-    <t>Household and trial characterisation questions</t>
-  </si>
-  <si>
-    <t>Table 2. Household and trial characterisation questions </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tricot questions to assess crop genotypes  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Table 3 outlines the tricot questions that are asked to the experimenting farmer to capture comparative rankings of crop genotypes.  </t>
-  </si>
-  <si>
-    <t>Table 3. Tricot questions for variety ranking</t>
-  </si>
-  <si>
-    <t>Consumer Evaluation Survey for Boiled Sweet Potato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tables 4 and 5 outline the instructions and data to be collected to ensure accurate and consistent tasting of the sweet potato samples. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Table 4: Consumer evaluation questions  </t>
-  </si>
-  <si>
-    <t>Table 5: Tricot questions for variety ranking</t>
-  </si>
-  <si>
-    <t>Farmers' socio-economic characteristics</t>
-  </si>
-  <si>
-    <t>Table 6 outlines the questions that are going to be asked and help us in characterising the households.</t>
-  </si>
-  <si>
-    <t>The respondent should be the person in charge of the trial.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This document provides a standardised overview of the information that will be collected during a `r cropname` tricot trial. The protocol provides an overview of the data collection points during the trials, including the variables and traits collected at each crop stage. Farmers evaluate varieties in their on-farm trials and provide comparative observations by ranking the varieties based on their performance throughout their growth and post-harvest qualities, including taste and consumption preferences. A more in-depth overview of the steps required for developing an on-farm trial project using tricot and ClimMob is available here: https://learn.climmob.net/. </t>
-  </si>
-  <si>
     <t>consent-heading</t>
   </si>
   <si>
     <t>consent</t>
   </si>
   <si>
-    <t>data-heading</t>
-  </si>
-  <si>
-    <t>data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All plots (A, B, C) in the OFT must have the same dimensions and be placed side by side in the farmer’s field. Potential edge effects remain a research question. Therefore, we recommend calculating the yield for the entire plot, including edges, rather than solely focusing on the interior plants. </t>
+    <t>scope-heading</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>This informed consent form provides a standardised framework to ensure that all participants are adequately informed before taking part in the experiment and associated surveys. It explains the purpose of the data collection, the types of information that will be collected, and how these data may be used, including for research and publication. Participation is entirely voluntary. Participants may decline to answer any question or withdraw from the study at any time, without any negative consequences. Consent is obtained before data collection to ensure transparency, ethical research practice, and respect for participants’ rights. Providing informed consent is a prerequisite for inclusion in all subsequent trial and survey activities. Informed consent template is appended to this SOP.</t>
+  </si>
+  <si>
+    <t>scope</t>
+  </si>
+  <si>
+    <t>Selection of participants</t>
+  </si>
+  <si>
+    <t>Seed multiplication</t>
+  </si>
+  <si>
+    <t>Selection of genotypes</t>
+  </si>
+  <si>
+    <t>Selection of locations</t>
+  </si>
+  <si>
+    <t>https://learn.climmob.net/design/sampling-plots</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>Providing metadata for your trial</t>
+  </si>
+  <si>
+    <t>https://learn.climmob.net/design/trial_size</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>https://learn.climmob.net/design/trial_documentation</t>
+  </si>
+  <si>
+    <t>Data analysis</t>
+  </si>
+  <si>
+    <t>https://learn.climmob.net/analysis/intro-data-analysis</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>https://learn.climmob.net/preparation/budgeting</t>
+  </si>
+  <si>
+    <t>Check list for implementing on-farm trial</t>
+  </si>
+  <si>
+    <t>https://learn.climmob.net/preparation/checklist</t>
+  </si>
+  <si>
+    <t>Yield estimation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This document provides an overview of the information that will be collected during an on-farm trial with the tricot approach. The protocol provides an overview of the data collection points during the trials, including the variables and traits collected at each crop stage. Farmers evaluate varieties in their on-farm trials and provide comparative observations by ranking the varieties based on their relative performance throughout their growth and post-harvest qualities. A more in-depth overview of the steps required for developing a participatory on-farm trial using tricot is available here https://learn.climmob.net/. </t>
+  </si>
+  <si>
+    <t>Orçamento</t>
+  </si>
+  <si>
+    <t>Seleção de participantes</t>
+  </si>
+  <si>
+    <t>Multiplicação de sementes</t>
+  </si>
+  <si>
+    <t>Análise de dados</t>
+  </si>
+  <si>
+    <t>Check list para implementar ensaios em fazendas de produtores</t>
+  </si>
+  <si>
+    <t>Metadados do ensaio experimental</t>
+  </si>
+  <si>
+    <t>Seleção de genótipos para o ensaio experimental</t>
+  </si>
+  <si>
+    <t>Seleção de sítios de ensaio experimental</t>
+  </si>
+  <si>
+    <t>Trial design</t>
+  </si>
+  <si>
+    <t>design-heading</t>
+  </si>
+  <si>
+    <t>design</t>
+  </si>
+  <si>
+    <t>All plots are labelled using letters (A, B, and C). Plots should be established on the same planting date and follow the same plot dimensions and management practices. Plot size should follow recommendations from the local implementing team and be appropriate for the crop and farming system. Information on plot dimensions should be recorded in the trial metadata. The three plots should be located within the same field whenever possible to ensure exposure to similar environmental and management conditions. If sufficient land is available, farmers are encouraged to establish an additional plot of their preferred or commonly grown local variety ("Local") using the same planting date, plot size, and management practices. Although the Local plot is not part of the core tricot design, it may be included in the end-of-season evaluation, where participants are asked whether the local variety performed better or worse than options A, B, and C.</t>
+  </si>
+  <si>
+    <t>materials-heading</t>
+  </si>
+  <si>
+    <t>Materials and equipment</t>
+  </si>
+  <si>
+    <t>Data collection in tricot trials may be conducted using either digital surveys administered by field staff or observation cards completed by participants. Depending on the selected data collection approach, the following materials and equipment may be required.</t>
+  </si>
+  <si>
+    <t>**Coverage:** This SOP describes the procedures and standards for implementing decentralized participatory on-farm trials using the tricot approach. It covers the evaluation design, documentation, monitoring, and data management of tricot trials. The SOP includes guidance on digital survey configuration, data collection, metadata standards, and basic quality assurance procedures to support FAIR data generation. This SOP is intended to support standardized implementation of tricot trials while allowing contextual adaptation to local crops, farming systems, languages, and institutional settings.</t>
+  </si>
+  <si>
+    <t>**Exclusions:** This SOP does not cover guidance on selection of genotypes, selection of participants, advanced statistical analysis, breeding decision-making workflows, laboratory analysis procedures, seed multiplication and certification protocols. Specific procedures related to genomic analysis, climate modelling, seed shipment regulations, or laboratory phenotyping should be addressed in separate SOPs where applicable.</t>
+  </si>
+  <si>
+    <t>**Intended audience:** This SOP is intended for breeders, agronomists, genebank staff, NGOs, farmer organizations, students, and researchers involved in the implementation, coordination, and management of tricot trials and decentralized participatory experimentation.</t>
+  </si>
+  <si>
+    <t>**Digital data collection (ODK):** i) Android smartphone or tablet with sufficient battery capacity; ii) ODK Collect application installed and configured; iii) Internet connection for downloading and submitting forms (when available); iv) Power bank or charging equipment for fieldwork; v) Participant lists and trial allocation records.</t>
+  </si>
+  <si>
+    <t>**Observation card-based data collection:** i) Printed trial observation cards; ii) Pens or pencils for participants; iii) Trial labels identifying options A, B, and C; iv) Participant lists and trial allocation records.</t>
+  </si>
+  <si>
+    <t>**Data entry and compilation:** i) Computer with internet access; ii) Access to the ClimMob platform; iii) Enketo web forms for direct data entry or iv) ClimMob Excel templates for offline data entry and subsequent upload.</t>
+  </si>
+  <si>
+    <t>Project teams should select the data collection method most appropriate for local conditions, participant preferences, and available resources.</t>
+  </si>
+  <si>
+    <t>materials</t>
+  </si>
+  <si>
+    <t>Participants observe their assigned plots throughout the trial and record their observations at predefined data collection moments (crop growth stages). Data may be collected directly by field technicians using ODK on Android devices or recorded by participants on trial observation cards and subsequently digitized in ClimMob using Enketo forms or Excel templates. This SOP defines the observation moments, which are aligned with crop development stages and should be clearly communicated to participants during the distribution of the trial package and throughout the trial period. Observation cards should contain simple comparison questions that allow participants to identify the best and worst option for each evaluation criterion. Participants should be encouraged to focus on one criterion at a time when making their assessments. Project teams are encouraged to provide follow-up support through field visits, phone calls, or other communication channels to remind participants of upcoming observations, answer questions, and support timely data collection.</t>
+  </si>
+  <si>
+    <t>trial-observation-heading</t>
+  </si>
+  <si>
+    <t>Trial observation and data collection</t>
+  </si>
+  <si>
+    <t>trial-observation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -176,6 +252,20 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -197,20 +287,26 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -543,12 +639,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB5FF5ED-AA91-F847-8546-368AFFC4F6A2}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="72.6640625" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="10.83203125" style="2"/>
+    <col min="1" max="1" width="31.33203125" customWidth="1"/>
+    <col min="2" max="2" width="91" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -575,198 +670,324 @@
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="136" x14ac:dyDescent="0.2">
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="B3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" ht="138" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="B9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
     </row>
     <row r="10" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" ht="170" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>15</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
     </row>
     <row r="12" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>19</v>
+        <v>57</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>21</v>
+        <v>57</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>30</v>
+        <v>59</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="170" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4041A62-4750-304C-A0F2-6428C3DB8928}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="34" customWidth="1"/>
+    <col min="6" max="6" width="46" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F4" r:id="rId1" xr:uid="{091EF056-F7D3-3D44-B38F-036BC5B82013}"/>
+    <hyperlink ref="F5" r:id="rId2" xr:uid="{3419D782-D4DB-6445-89A4-8D5F2C3018D1}"/>
+    <hyperlink ref="F8" r:id="rId3" xr:uid="{D3F4B49F-331D-2942-9547-B8BB03FAB832}"/>
+    <hyperlink ref="F3" r:id="rId4" xr:uid="{551D5D88-8D8C-224A-AD7D-AEBBF5803942}"/>
+    <hyperlink ref="F2" r:id="rId5" xr:uid="{F10D30FF-5464-7A45-A3B6-5104D119D0D8}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/base-text-sop.xlsx
+++ b/data/base-text-sop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-protocols/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACFAA29F-15CA-5D4A-96D1-FE44D0CFA79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C510A6-1F45-C04E-9A54-CEC53AF022F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="60" yWindow="600" windowWidth="30660" windowHeight="16980" xr2:uid="{CCA2DD50-73A2-AB48-A73E-30174A4C4548}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="74">
   <si>
     <t>en</t>
   </si>
@@ -235,6 +235,42 @@
   </si>
   <si>
     <t>trial-observation</t>
+  </si>
+  <si>
+    <t>Participant registration is conducted during the distribution of trial packages and should be completed for all participants before any subsequent data collection activities can take place. Trial packages should be distributed sufficiently in advance of planting to allow participants adequate time for land preparation and trial establishment. The purpose of registration is to link each participant to a unique trial package and collect the minimum information required for trial management and participant follow-up. Registration activities should remain as brief and efficient as possible, as package distribution is often a busy activity during which project staff must distribute trial materials, explain trial procedures, answer participant questions, and provide implementation guidance. **Completion of participant registration is mandatory for inclusion in subsequent data collection activities and analyses.** During registration, project staff should explain the trial objectives, plot establishment procedures, observation schedule, and participant responsibilities throughout the duration of the trial.</t>
+  </si>
+  <si>
+    <t>Participant registration</t>
+  </si>
+  <si>
+    <t>registration-heading</t>
+  </si>
+  <si>
+    <t>registration</t>
+  </si>
+  <si>
+    <t>The socio-economic survey collects information on participant characteristics, household composition, farming activities, crop management practices, seed systems, market participation, and access to agricultural services. The purpose of this survey is to identify socio-economic factors associated with crop variety management and farmer preferences, and to support the interpretation of trial results across different participant groups. Because the socio-economic survey is more comprehensive than the participant registration form, it does not need to be administered at the same time as trial package distribution. The survey may be conducted during follow-up visits, or at any suitable moment during the trial period. Project teams may administer the survey to different groups of participants throughout the duration of the trial according to available resources and operational constraints. Although completion of the socio-economic survey is encouraged for all participants, project teams may prioritize a representative subset of participants when resources are limited. The survey should be completed before final data analysis whenever possible to enable the integration of socio-economic information with trial observations and participant evaluations.</t>
+  </si>
+  <si>
+    <t>socioeconomic</t>
+  </si>
+  <si>
+    <t>Socio-economic data</t>
+  </si>
+  <si>
+    <t>socioeconomic-heading</t>
+  </si>
+  <si>
+    <t>survey-heading</t>
+  </si>
+  <si>
+    <t>Survey components</t>
+  </si>
+  <si>
+    <t>survey</t>
+  </si>
+  <si>
+    <t>The tricot data collection framework is composed of multiple survey components implemented throughout the duration of the trial. These components collect complementary information required for trial management, participant follow-up, characterization of trial conditions, and evaluation of technology performance. Data collection begins with participant registration and informed consent, followed by crop-stage observations recorded throughout the trial. Depending on project objectives and available resources, additional socio-economic information may be collected from all participants or from a representative subset of participants. At the end of the trial, participants complete final evaluations of the tested technologies, including post-harvest observations. The following sections provide the complete list of variables, questions, and data collection moments associated with this tricot protocol. This survey is available on ClimMob as a project template named `r templatename`.</t>
   </si>
 </sst>
 </file>
@@ -291,13 +327,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -639,11 +672,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB5FF5ED-AA91-F847-8546-368AFFC4F6A2}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.33203125" customWidth="1"/>
-    <col min="2" max="2" width="91" customWidth="1"/>
+    <col min="1" max="1" width="31.33203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="91" style="3" customWidth="1"/>
+    <col min="3" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -670,129 +704,90 @@
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
     </row>
     <row r="3" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:6" ht="85" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
     </row>
     <row r="9" spans="1:6" ht="138" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
     </row>
     <row r="10" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
     </row>
     <row r="11" spans="1:6" ht="170" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
     </row>
     <row r="12" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>48</v>
       </c>
     </row>
@@ -800,7 +795,7 @@
       <c r="A13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>49</v>
       </c>
     </row>
@@ -808,7 +803,7 @@
       <c r="A14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>53</v>
       </c>
     </row>
@@ -816,7 +811,7 @@
       <c r="A15" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>54</v>
       </c>
     </row>
@@ -824,7 +819,7 @@
       <c r="A16" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>55</v>
       </c>
     </row>
@@ -832,7 +827,7 @@
       <c r="A17" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>56</v>
       </c>
     </row>
@@ -840,16 +835,64 @@
       <c r="A18" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="170" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+    <row r="19" spans="1:2" ht="180" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="4" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="204" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="238" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="187" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -894,7 +937,7 @@
       <c r="B2" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>32</v>
       </c>
     </row>
@@ -905,7 +948,7 @@
       <c r="B3" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>30</v>
       </c>
     </row>
@@ -916,7 +959,7 @@
       <c r="B4" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -927,7 +970,7 @@
       <c r="B5" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -960,7 +1003,7 @@
       <c r="B8" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="2" t="s">
         <v>26</v>
       </c>
     </row>

--- a/data/base-text-sop.xlsx
+++ b/data/base-text-sop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-protocols/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C510A6-1F45-C04E-9A54-CEC53AF022F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7EDAC46-90A1-2E42-8EB1-0D3EB0818487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="60" yWindow="600" windowWidth="30660" windowHeight="16980" xr2:uid="{CCA2DD50-73A2-AB48-A73E-30174A4C4548}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="79">
   <si>
     <t>en</t>
   </si>
@@ -271,6 +271,21 @@
   </si>
   <si>
     <t>The tricot data collection framework is composed of multiple survey components implemented throughout the duration of the trial. These components collect complementary information required for trial management, participant follow-up, characterization of trial conditions, and evaluation of technology performance. Data collection begins with participant registration and informed consent, followed by crop-stage observations recorded throughout the trial. Depending on project objectives and available resources, additional socio-economic information may be collected from all participants or from a representative subset of participants. At the end of the trial, participants complete final evaluations of the tested technologies, including post-harvest observations. The following sections provide the complete list of variables, questions, and data collection moments associated with this tricot protocol. This survey is available on ClimMob as a project template named `r templatename`.</t>
+  </si>
+  <si>
+    <t>Coleta de dados de rendimento</t>
+  </si>
+  <si>
+    <t>other-heading</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>The following table provide additional guidance and SOPs for planning, implementing, documenting, and analysing tricot trials.</t>
+  </si>
+  <si>
+    <t>Other resources and SOPs</t>
   </si>
 </sst>
 </file>
@@ -672,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB5FF5ED-AA91-F847-8546-368AFFC4F6A2}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.33203125" style="3" customWidth="1"/>
@@ -895,6 +910,22 @@
         <v>73</v>
       </c>
     </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -905,131 +936,134 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="34" customWidth="1"/>
-    <col min="6" max="6" width="46" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="34" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>30</v>
-      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>42</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
         <v>19</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>41</v>
-      </c>
-      <c r="F6" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>37</v>
       </c>
-      <c r="F7" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="A8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
         <v>23</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>40</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
         <v>27</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>38</v>
       </c>
-      <c r="F9" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F4" r:id="rId1" xr:uid="{091EF056-F7D3-3D44-B38F-036BC5B82013}"/>
-    <hyperlink ref="F5" r:id="rId2" xr:uid="{3419D782-D4DB-6445-89A4-8D5F2C3018D1}"/>
-    <hyperlink ref="F8" r:id="rId3" xr:uid="{D3F4B49F-331D-2942-9547-B8BB03FAB832}"/>
-    <hyperlink ref="F3" r:id="rId4" xr:uid="{551D5D88-8D8C-224A-AD7D-AEBBF5803942}"/>
-    <hyperlink ref="F2" r:id="rId5" xr:uid="{F10D30FF-5464-7A45-A3B6-5104D119D0D8}"/>
+    <hyperlink ref="A4" r:id="rId1" xr:uid="{091EF056-F7D3-3D44-B38F-036BC5B82013}"/>
+    <hyperlink ref="A5" r:id="rId2" xr:uid="{3419D782-D4DB-6445-89A4-8D5F2C3018D1}"/>
+    <hyperlink ref="A8" r:id="rId3" xr:uid="{D3F4B49F-331D-2942-9547-B8BB03FAB832}"/>
+    <hyperlink ref="A3" r:id="rId4" xr:uid="{551D5D88-8D8C-224A-AD7D-AEBBF5803942}"/>
+    <hyperlink ref="A2" r:id="rId5" xr:uid="{F10D30FF-5464-7A45-A3B6-5104D119D0D8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/base-text-sop.xlsx
+++ b/data/base-text-sop.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-protocols/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7EDAC46-90A1-2E42-8EB1-0D3EB0818487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAEC288-D542-464E-82F0-A8C29729AC4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="600" windowWidth="30660" windowHeight="16980" xr2:uid="{CCA2DD50-73A2-AB48-A73E-30174A4C4548}"/>
+    <workbookView xWindow="13420" yWindow="600" windowWidth="17300" windowHeight="16980" xr2:uid="{CCA2DD50-73A2-AB48-A73E-30174A4C4548}"/>
   </bookViews>
   <sheets>
-    <sheet name="text" sheetId="1" r:id="rId1"/>
-    <sheet name="other_resources" sheetId="2" r:id="rId2"/>
+    <sheet name="title" sheetId="3" r:id="rId1"/>
+    <sheet name="text" sheetId="1" r:id="rId2"/>
+    <sheet name="other_resources" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_Toc219906839" localSheetId="0">text!$A$8</definedName>
-    <definedName name="_Toc219906845" localSheetId="0">text!#REF!</definedName>
-    <definedName name="_Toc219906846" localSheetId="0">text!#REF!</definedName>
-    <definedName name="_Toc219906847" localSheetId="0">text!#REF!</definedName>
-    <definedName name="_Toc219906848" localSheetId="0">text!#REF!</definedName>
-    <definedName name="_Toc219906849" localSheetId="0">text!#REF!</definedName>
-    <definedName name="_Toc219906850" localSheetId="0">text!#REF!</definedName>
+    <definedName name="_Toc219906839" localSheetId="1">text!$A$8</definedName>
+    <definedName name="_Toc219906845" localSheetId="1">text!#REF!</definedName>
+    <definedName name="_Toc219906846" localSheetId="1">text!#REF!</definedName>
+    <definedName name="_Toc219906847" localSheetId="1">text!#REF!</definedName>
+    <definedName name="_Toc219906848" localSheetId="1">text!#REF!</definedName>
+    <definedName name="_Toc219906849" localSheetId="1">text!#REF!</definedName>
+    <definedName name="_Toc219906850" localSheetId="1">text!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="113">
   <si>
     <t>en</t>
   </si>
@@ -96,9 +97,6 @@
     <t>Scope</t>
   </si>
   <si>
-    <t>This informed consent form provides a standardised framework to ensure that all participants are adequately informed before taking part in the experiment and associated surveys. It explains the purpose of the data collection, the types of information that will be collected, and how these data may be used, including for research and publication. Participation is entirely voluntary. Participants may decline to answer any question or withdraw from the study at any time, without any negative consequences. Consent is obtained before data collection to ensure transparency, ethical research practice, and respect for participants’ rights. Providing informed consent is a prerequisite for inclusion in all subsequent trial and survey activities. Informed consent template is appended to this SOP.</t>
-  </si>
-  <si>
     <t>scope</t>
   </si>
   <si>
@@ -237,9 +235,6 @@
     <t>trial-observation</t>
   </si>
   <si>
-    <t>Participant registration is conducted during the distribution of trial packages and should be completed for all participants before any subsequent data collection activities can take place. Trial packages should be distributed sufficiently in advance of planting to allow participants adequate time for land preparation and trial establishment. The purpose of registration is to link each participant to a unique trial package and collect the minimum information required for trial management and participant follow-up. Registration activities should remain as brief and efficient as possible, as package distribution is often a busy activity during which project staff must distribute trial materials, explain trial procedures, answer participant questions, and provide implementation guidance. **Completion of participant registration is mandatory for inclusion in subsequent data collection activities and analyses.** During registration, project staff should explain the trial objectives, plot establishment procedures, observation schedule, and participant responsibilities throughout the duration of the trial.</t>
-  </si>
-  <si>
     <t>Participant registration</t>
   </si>
   <si>
@@ -255,9 +250,6 @@
     <t>socioeconomic</t>
   </si>
   <si>
-    <t>Socio-economic data</t>
-  </si>
-  <si>
     <t>socioeconomic-heading</t>
   </si>
   <si>
@@ -286,6 +278,117 @@
   </si>
   <si>
     <t>Other resources and SOPs</t>
+  </si>
+  <si>
+    <t>The informed consent form provides a standardized framework to ensure that all participants are adequately informed before taking part in the experiment and associated surveys. It explains the purpose of the data collection, the types of information that will be collected, and how these data may be used, including for research and publication. Participation is entirely voluntary. Participants may decline to answer any question or withdraw from the study at any time, without any negative consequences. Consent is obtained before data collection to ensure transparency, ethical research practice, and respect for participants’ rights. Providing informed consent is a prerequisite for inclusion in all subsequent trial and survey activities. Informed consent template is appended to this SOP.</t>
+  </si>
+  <si>
+    <t>Socio-economic survey</t>
+  </si>
+  <si>
+    <t>Participant registration is conducted during the distribution of trial packages and should be completed for all participants before any subsequent data collection activities can take place. Trial packages should be distributed sufficiently in advance of planting to allow participants adequate time for land preparation and trial establishment. The purpose of registration is to link each participant to a unique trial package and collect the minimum information required for trial management and participant follow-up. Registration activities should remain as brief and efficient as possible, as package distribution is often a busy activity during which project staff must distribute trial materials, explain trial procedures, answer participant questions, and provide implementation guidance. Completion of participant registration is mandatory for inclusion in subsequent data collection activities and analyses. During registration, project staff should explain the trial objectives, plot establishment procedures, observation schedule, and participant responsibilities throughout the duration of the trial.</t>
+  </si>
+  <si>
+    <t>Escopo</t>
+  </si>
+  <si>
+    <t>Este documento fornece uma visão geral das informações que serão coletadas durante um ensaio em campo com a abordagem tricot. O protocolo apresenta os pontos de coleta de dados durante os ensaios, incluindo as variáveis ​​e características coletadas em cada estágio da cultura. Os agricultores avaliam as variedades em seus ensaios em campo e fornecem observações comparativas, classificando-as com base em seu desempenho relativo ao longo do crescimento e em suas qualidades pós-colheita. Uma visão geral mais detalhada das etapas necessárias para o desenvolvimento de um ensaio participativo em campo usando a abordagem tricot está disponível no seguinte link: https://learn.climmob.net/.</t>
+  </si>
+  <si>
+    <t>**Exclusões:** Este SOP não abrange orientações sobre seleção de genótipos, seleção de participantes, análise estatística avançada, fluxos de trabalho para tomada de decisão em melhoramento genético, procedimentos de análise laboratorial, multiplicação de sementes e protocolos de certificação. Procedimentos específicos relacionados à análise genômica, modelagem climática, regulamentações para envio de sementes ou fenotipagem laboratorial devem ser abordados em SOPs separados, quando aplicável.</t>
+  </si>
+  <si>
+    <t>**Público-alvo:** Este SOP destina-se a melhoristas, agrônomos, funcionários de bancos de germoplasma, ONGs, organizações de agricultores, estudantes e pesquisadores envolvidos na implementação, coordenação e gestão de ensaios de tricotomia e experimentação participativa descentralizada.</t>
+  </si>
+  <si>
+    <t>**Abrangência:** Este SOP descreve os procedimentos e padrões para a implementação de ensaios participativos descentralizados em propriedades rurais utilizando a abordagem tricot. Abrange o planejamento da avaliação, a documentação, o monitoramento e o gerenciamento de dados dos ensaios tricot. O SOP inclui orientações sobre a configuração de questionários digitais, a coleta de dados, os padrões de metadados e os procedimentos básicos de garantia da qualidade para apoiar a geração de dados FAIR. Este SOP visa apoiar a implementação padronizada de ensaios tricot, permitindo, ao mesmo tempo, a adaptação contextual às culturas locais, aos sistemas agrícolas, aos idiomas e aos contextos institucionais.</t>
+  </si>
+  <si>
+    <t>Consentimento</t>
+  </si>
+  <si>
+    <t>O formulário de consentimento livre e esclarecido fornece uma estrutura padronizada para garantir que todos os participantes sejam adequadamente informados antes de participar do experimento e das pesquisas associadas. Ele explica a finalidade da coleta de dados, os tipos de informações que serão coletadas e como esses dados poderão ser usados, inclusive para pesquisa e publicação. A participação é inteiramente voluntária. Os participantes podem se recusar a responder a qualquer pergunta ou desistir do estudo a qualquer momento, sem quaisquer consequências negativas. O consentimento é obtido antes da coleta de dados para garantir transparência, práticas de pesquisa éticas e respeito aos direitos dos participantes. O fornecimento do consentimento livre e esclarecido é um pré-requisito para a inclusão em todas as atividades subsequentes do ensaio clínico e das pesquisas. O modelo de consentimento livre e esclarecido está anexado a este SOP.</t>
+  </si>
+  <si>
+    <t>Desenho experimental</t>
+  </si>
+  <si>
+    <t>Todas as parcelas são identificadas pelas letras A, B e C. As parcelas devem ser estabelecidas na mesma data de plantio e seguir as mesmas dimensões e práticas de manejo. O tamanho das parcelas deve seguir as recomendações da equipe de implementação local e ser adequado à cultura e ao sistema de cultivo. As informações sobre as dimensões das parcelas devem ser registradas nos metadados do ensaio. As três parcelas devem ser localizadas no mesmo campo, sempre que possível, para garantir a exposição a condições ambientais e de manejo semelhantes. Se houver área suficiente disponível, os agricultores são incentivados a estabelecer uma parcela adicional de sua variedade local preferida ou comumente cultivada ("Local"), utilizando a mesma data de plantio, tamanho e práticas de manejo. Embora a parcela Local não faça parte do delineamento principal do experimento, ela pode ser incluída na avaliação de final de safra, na qual os participantes são questionados sobre se a variedade local apresentou desempenho melhor ou pior do que as opções A, B e C.</t>
+  </si>
+  <si>
+    <t>Standard operating procedures for data collection and implementation of on-farm trials with the tricot approach</t>
+  </si>
+  <si>
+    <t>Procedimentos operacionais padrão para coleta de dados e implementação de ensaios experimentais em fazendas com a abordagem tricot</t>
+  </si>
+  <si>
+    <t>Versão</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>Crop</t>
+  </si>
+  <si>
+    <t>Taxa</t>
+  </si>
+  <si>
+    <t>Authors</t>
+  </si>
+  <si>
+    <t>Institutions</t>
+  </si>
+  <si>
+    <t>Traits</t>
+  </si>
+  <si>
+    <t>Data collection moments</t>
+  </si>
+  <si>
+    <t>Cultivo</t>
+  </si>
+  <si>
+    <t>Taxonomia</t>
+  </si>
+  <si>
+    <t>Autores</t>
+  </si>
+  <si>
+    <t>Instituições</t>
+  </si>
+  <si>
+    <t>Atributos</t>
+  </si>
+  <si>
+    <t>Estádios de coleta de dados</t>
+  </si>
+  <si>
+    <t>Question name</t>
+  </si>
+  <si>
+    <t>Question description</t>
+  </si>
+  <si>
+    <t>Nome da pergunta</t>
+  </si>
+  <si>
+    <t>Descrição</t>
+  </si>
+  <si>
+    <t>Resource</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Recurso</t>
+  </si>
+  <si>
+    <t>This document is also available in</t>
+  </si>
+  <si>
+    <t>Este documento também está disponível em</t>
   </si>
 </sst>
 </file>
@@ -342,7 +445,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
@@ -351,6 +454,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -686,244 +792,133 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB5FF5ED-AA91-F847-8546-368AFFC4F6A2}">
-  <dimension ref="A1:F27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70DB7E77-C0DE-BB4E-8530-DD7ED990578A}">
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.33203125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="91" style="3" customWidth="1"/>
-    <col min="3" max="16384" width="10.83203125" style="3"/>
+    <col min="1" max="1" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:5" ht="102" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="138" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="170" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="180" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="204" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="238" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="187" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -932,6 +927,280 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB5FF5ED-AA91-F847-8546-368AFFC4F6A2}">
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="31.33203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="49.83203125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="43.6640625" style="4" customWidth="1"/>
+    <col min="4" max="16384" width="10.83203125" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="251" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="306" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="221" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="136" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="404" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="102" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="119" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="180" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="372" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="340" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4041A62-4750-304C-A0F2-6428C3DB8928}">
   <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -943,7 +1212,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -963,98 +1232,98 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/data/base-text-sop.xlsx
+++ b/data/base-text-sop.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-protocols/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAEC288-D542-464E-82F0-A8C29729AC4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E366FB0-405C-0C45-9517-9E9AEF8688A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13420" yWindow="600" windowWidth="17300" windowHeight="16980" xr2:uid="{CCA2DD50-73A2-AB48-A73E-30174A4C4548}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="16700" xr2:uid="{CCA2DD50-73A2-AB48-A73E-30174A4C4548}"/>
   </bookViews>
   <sheets>
     <sheet name="title" sheetId="3" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="143">
   <si>
     <t>en</t>
   </si>
@@ -136,9 +136,6 @@
     <t>https://learn.climmob.net/analysis/intro-data-analysis</t>
   </si>
   <si>
-    <t>Budget</t>
-  </si>
-  <si>
     <t>https://learn.climmob.net/preparation/budgeting</t>
   </si>
   <si>
@@ -151,12 +148,6 @@
     <t>Yield estimation</t>
   </si>
   <si>
-    <t xml:space="preserve">This document provides an overview of the information that will be collected during an on-farm trial with the tricot approach. The protocol provides an overview of the data collection points during the trials, including the variables and traits collected at each crop stage. Farmers evaluate varieties in their on-farm trials and provide comparative observations by ranking the varieties based on their relative performance throughout their growth and post-harvest qualities. A more in-depth overview of the steps required for developing a participatory on-farm trial using tricot is available here https://learn.climmob.net/. </t>
-  </si>
-  <si>
-    <t>Orçamento</t>
-  </si>
-  <si>
     <t>Seleção de participantes</t>
   </si>
   <si>
@@ -187,9 +178,6 @@
     <t>design</t>
   </si>
   <si>
-    <t>All plots are labelled using letters (A, B, and C). Plots should be established on the same planting date and follow the same plot dimensions and management practices. Plot size should follow recommendations from the local implementing team and be appropriate for the crop and farming system. Information on plot dimensions should be recorded in the trial metadata. The three plots should be located within the same field whenever possible to ensure exposure to similar environmental and management conditions. If sufficient land is available, farmers are encouraged to establish an additional plot of their preferred or commonly grown local variety ("Local") using the same planting date, plot size, and management practices. Although the Local plot is not part of the core tricot design, it may be included in the end-of-season evaluation, where participants are asked whether the local variety performed better or worse than options A, B, and C.</t>
-  </si>
-  <si>
     <t>materials-heading</t>
   </si>
   <si>
@@ -223,9 +211,6 @@
     <t>materials</t>
   </si>
   <si>
-    <t>Participants observe their assigned plots throughout the trial and record their observations at predefined data collection moments (crop growth stages). Data may be collected directly by field technicians using ODK on Android devices or recorded by participants on trial observation cards and subsequently digitized in ClimMob using Enketo forms or Excel templates. This SOP defines the observation moments, which are aligned with crop development stages and should be clearly communicated to participants during the distribution of the trial package and throughout the trial period. Observation cards should contain simple comparison questions that allow participants to identify the best and worst option for each evaluation criterion. Participants should be encouraged to focus on one criterion at a time when making their assessments. Project teams are encouraged to provide follow-up support through field visits, phone calls, or other communication channels to remind participants of upcoming observations, answer questions, and support timely data collection.</t>
-  </si>
-  <si>
     <t>trial-observation-heading</t>
   </si>
   <si>
@@ -244,9 +229,6 @@
     <t>registration</t>
   </si>
   <si>
-    <t>The socio-economic survey collects information on participant characteristics, household composition, farming activities, crop management practices, seed systems, market participation, and access to agricultural services. The purpose of this survey is to identify socio-economic factors associated with crop variety management and farmer preferences, and to support the interpretation of trial results across different participant groups. Because the socio-economic survey is more comprehensive than the participant registration form, it does not need to be administered at the same time as trial package distribution. The survey may be conducted during follow-up visits, or at any suitable moment during the trial period. Project teams may administer the survey to different groups of participants throughout the duration of the trial according to available resources and operational constraints. Although completion of the socio-economic survey is encouraged for all participants, project teams may prioritize a representative subset of participants when resources are limited. The survey should be completed before final data analysis whenever possible to enable the integration of socio-economic information with trial observations and participant evaluations.</t>
-  </si>
-  <si>
     <t>socioeconomic</t>
   </si>
   <si>
@@ -262,9 +244,6 @@
     <t>survey</t>
   </si>
   <si>
-    <t>The tricot data collection framework is composed of multiple survey components implemented throughout the duration of the trial. These components collect complementary information required for trial management, participant follow-up, characterization of trial conditions, and evaluation of technology performance. Data collection begins with participant registration and informed consent, followed by crop-stage observations recorded throughout the trial. Depending on project objectives and available resources, additional socio-economic information may be collected from all participants or from a representative subset of participants. At the end of the trial, participants complete final evaluations of the tested technologies, including post-harvest observations. The following sections provide the complete list of variables, questions, and data collection moments associated with this tricot protocol. This survey is available on ClimMob as a project template named `r templatename`.</t>
-  </si>
-  <si>
     <t>Coleta de dados de rendimento</t>
   </si>
   <si>
@@ -280,48 +259,15 @@
     <t>Other resources and SOPs</t>
   </si>
   <si>
-    <t>The informed consent form provides a standardized framework to ensure that all participants are adequately informed before taking part in the experiment and associated surveys. It explains the purpose of the data collection, the types of information that will be collected, and how these data may be used, including for research and publication. Participation is entirely voluntary. Participants may decline to answer any question or withdraw from the study at any time, without any negative consequences. Consent is obtained before data collection to ensure transparency, ethical research practice, and respect for participants’ rights. Providing informed consent is a prerequisite for inclusion in all subsequent trial and survey activities. Informed consent template is appended to this SOP.</t>
-  </si>
-  <si>
-    <t>Socio-economic survey</t>
-  </si>
-  <si>
-    <t>Participant registration is conducted during the distribution of trial packages and should be completed for all participants before any subsequent data collection activities can take place. Trial packages should be distributed sufficiently in advance of planting to allow participants adequate time for land preparation and trial establishment. The purpose of registration is to link each participant to a unique trial package and collect the minimum information required for trial management and participant follow-up. Registration activities should remain as brief and efficient as possible, as package distribution is often a busy activity during which project staff must distribute trial materials, explain trial procedures, answer participant questions, and provide implementation guidance. Completion of participant registration is mandatory for inclusion in subsequent data collection activities and analyses. During registration, project staff should explain the trial objectives, plot establishment procedures, observation schedule, and participant responsibilities throughout the duration of the trial.</t>
-  </si>
-  <si>
     <t>Escopo</t>
   </si>
   <si>
-    <t>Este documento fornece uma visão geral das informações que serão coletadas durante um ensaio em campo com a abordagem tricot. O protocolo apresenta os pontos de coleta de dados durante os ensaios, incluindo as variáveis ​​e características coletadas em cada estágio da cultura. Os agricultores avaliam as variedades em seus ensaios em campo e fornecem observações comparativas, classificando-as com base em seu desempenho relativo ao longo do crescimento e em suas qualidades pós-colheita. Uma visão geral mais detalhada das etapas necessárias para o desenvolvimento de um ensaio participativo em campo usando a abordagem tricot está disponível no seguinte link: https://learn.climmob.net/.</t>
-  </si>
-  <si>
-    <t>**Exclusões:** Este SOP não abrange orientações sobre seleção de genótipos, seleção de participantes, análise estatística avançada, fluxos de trabalho para tomada de decisão em melhoramento genético, procedimentos de análise laboratorial, multiplicação de sementes e protocolos de certificação. Procedimentos específicos relacionados à análise genômica, modelagem climática, regulamentações para envio de sementes ou fenotipagem laboratorial devem ser abordados em SOPs separados, quando aplicável.</t>
-  </si>
-  <si>
-    <t>**Público-alvo:** Este SOP destina-se a melhoristas, agrônomos, funcionários de bancos de germoplasma, ONGs, organizações de agricultores, estudantes e pesquisadores envolvidos na implementação, coordenação e gestão de ensaios de tricotomia e experimentação participativa descentralizada.</t>
-  </si>
-  <si>
-    <t>**Abrangência:** Este SOP descreve os procedimentos e padrões para a implementação de ensaios participativos descentralizados em propriedades rurais utilizando a abordagem tricot. Abrange o planejamento da avaliação, a documentação, o monitoramento e o gerenciamento de dados dos ensaios tricot. O SOP inclui orientações sobre a configuração de questionários digitais, a coleta de dados, os padrões de metadados e os procedimentos básicos de garantia da qualidade para apoiar a geração de dados FAIR. Este SOP visa apoiar a implementação padronizada de ensaios tricot, permitindo, ao mesmo tempo, a adaptação contextual às culturas locais, aos sistemas agrícolas, aos idiomas e aos contextos institucionais.</t>
-  </si>
-  <si>
     <t>Consentimento</t>
   </si>
   <si>
-    <t>O formulário de consentimento livre e esclarecido fornece uma estrutura padronizada para garantir que todos os participantes sejam adequadamente informados antes de participar do experimento e das pesquisas associadas. Ele explica a finalidade da coleta de dados, os tipos de informações que serão coletadas e como esses dados poderão ser usados, inclusive para pesquisa e publicação. A participação é inteiramente voluntária. Os participantes podem se recusar a responder a qualquer pergunta ou desistir do estudo a qualquer momento, sem quaisquer consequências negativas. O consentimento é obtido antes da coleta de dados para garantir transparência, práticas de pesquisa éticas e respeito aos direitos dos participantes. O fornecimento do consentimento livre e esclarecido é um pré-requisito para a inclusão em todas as atividades subsequentes do ensaio clínico e das pesquisas. O modelo de consentimento livre e esclarecido está anexado a este SOP.</t>
-  </si>
-  <si>
     <t>Desenho experimental</t>
   </si>
   <si>
-    <t>Todas as parcelas são identificadas pelas letras A, B e C. As parcelas devem ser estabelecidas na mesma data de plantio e seguir as mesmas dimensões e práticas de manejo. O tamanho das parcelas deve seguir as recomendações da equipe de implementação local e ser adequado à cultura e ao sistema de cultivo. As informações sobre as dimensões das parcelas devem ser registradas nos metadados do ensaio. As três parcelas devem ser localizadas no mesmo campo, sempre que possível, para garantir a exposição a condições ambientais e de manejo semelhantes. Se houver área suficiente disponível, os agricultores são incentivados a estabelecer uma parcela adicional de sua variedade local preferida ou comumente cultivada ("Local"), utilizando a mesma data de plantio, tamanho e práticas de manejo. Embora a parcela Local não faça parte do delineamento principal do experimento, ela pode ser incluída na avaliação de final de safra, na qual os participantes são questionados sobre se a variedade local apresentou desempenho melhor ou pior do que as opções A, B e C.</t>
-  </si>
-  <si>
-    <t>Standard operating procedures for data collection and implementation of on-farm trials with the tricot approach</t>
-  </si>
-  <si>
-    <t>Procedimentos operacionais padrão para coleta de dados e implementação de ensaios experimentais em fazendas com a abordagem tricot</t>
-  </si>
-  <si>
     <t>Versão</t>
   </si>
   <si>
@@ -331,9 +277,6 @@
     <t>Crop</t>
   </si>
   <si>
-    <t>Taxa</t>
-  </si>
-  <si>
     <t>Authors</t>
   </si>
   <si>
@@ -349,9 +292,6 @@
     <t>Cultivo</t>
   </si>
   <si>
-    <t>Taxonomia</t>
-  </si>
-  <si>
     <t>Autores</t>
   </si>
   <si>
@@ -389,6 +329,176 @@
   </si>
   <si>
     <t>Este documento também está disponível em</t>
+  </si>
+  <si>
+    <t>This document provides a comprehensive overview of the data to be collected during on-farm trials using the tricot approach and designed on ClimMob platform (https://climmob.net). The protocol outlines the key  data collection points throughout  the trials, including the variables and traits to be collected at each crop growth stage. Farmers evaluate varieties in their on-farm trials and provide comparative observations by ranking the varieties based on their relative performance throughout their growth and post-harvest qualities. A more in-depth overview of the steps required for developing a participatory on-farm trial using tricot is available here https://learn.climmob.net.</t>
+  </si>
+  <si>
+    <t>Budget for a tricot trial</t>
+  </si>
+  <si>
+    <t>Orçamento para um ensaio tricot</t>
+  </si>
+  <si>
+    <t>Consent is obtained before data collection to ensure transparency, ethical research practice, and respect for participants’ rights. Providing informed consent is a prerequisite for inclusion in all subsequent trial and survey activities. Informed consent template is appended to this SOP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The informed consent form provides a standardized framework to ensure that all participants are adequately informed before taking part in the experiment and associated surveys. It explains the purpose of the data collection, the types of information that will be collected, and how these data may be used, including for research and publication. Participation is entirely voluntary. Participants may decline to answer any question or withdraw from the study at any time, without any negative consequences. </t>
+  </si>
+  <si>
+    <t>Observation cards should contain simple comparison questions that allow participants to identify the best and worst option for each evaluation criterion. Participants should be encouraged to focus on one criterion at a time when making their assessments. Project teams are encouraged to provide follow-up support through field visits, phone calls, or other communication channels to remind participants of upcoming observations, answer questions, and support timely data collection.</t>
+  </si>
+  <si>
+    <t>Participant registration is conducted during the distribution of trial packages and should be completed for all participants before any subsequent data collection activities can take place. Trial packages should be distributed sufficiently in advance of planting to allow participants adequate time for land preparation and trial establishment. The purpose of registration is to link each participant to a unique trial package and collect the minimum information required for trial management and participant follow-up.</t>
+  </si>
+  <si>
+    <t>Registration activities should remain as brief and efficient as possible, as package distribution is often a busy activity during which project staff must distribute trial materials, explain trial procedures, answer participant questions, and provide implementation guidance. Completion of participant registration is mandatory for inclusion in subsequent data collection activities and analyses. During registration, project staff should explain the trial objectives, plot establishment procedures, observation schedule, and participant responsibilities throughout the duration of the trial.</t>
+  </si>
+  <si>
+    <t>Socio-economic baseline survey</t>
+  </si>
+  <si>
+    <t>The socio-economic baseline survey collects information on participant characteristics, household composition, farming activities, crop management practices, seed systems, market participation, and access to agricultural services. The purpose of this survey is to identify socio-economic factors associated with crop variety management and farmer preferences, and to support the interpretation of trial results across different participant groups.</t>
+  </si>
+  <si>
+    <t>Because the socio-economic survey is more comprehensive than the participant registration form, it does not need to be administered at the same time as trial package distribution. The survey may be conducted during follow-up visits, or at any suitable moment during the trial period. Project teams may administer the survey to different groups of participants throughout the duration of the trial according to available resources and operational constraints. Although completion of the socio-economic survey is encouraged for all participants, project teams may prioritize a representative subset of participants when resources are limited. The survey should be completed before final data analysis whenever possible to enable the integration of socio-economic information with trial observations and participant evaluations.</t>
+  </si>
+  <si>
+    <t>The tricot data collection framework is composed of multiple survey components implemented throughout the duration of the trial. These components collect complementary information required for trial management, participant follow-up, characterization of trial conditions, and evaluation of technology performance. Data collection begins with participant registration and informed consent, followed by crop-stage observations recorded throughout the trial. Depending on project objectives and available resources, additional socio-economic information may be collected from all participants or from a representative subset of participants.</t>
+  </si>
+  <si>
+    <t>At the end of the trial, participants complete final evaluations of the tested technologies, including post-harvest observations. The following sections provide the complete list of variables, questions, and data collection moments associated with this tricot protocol. This survey is available on ClimMob as a project template named `r templatename`.</t>
+  </si>
+  <si>
+    <t>Participants observe their assigned plots throughout the trial duration and record their observations at predefined data collection moments (crop growth stages). Data may be collected directly by field technicians using ODK on Android devices or recorded by participants on trial observation cards and subsequently digitized in ClimMob using Enketo forms or Excel templates. This SOP defines the observation moments, which are aligned with crop development stages and should be clearly communicated to participants during the distribution of the trial package and throughout the trial period.</t>
+  </si>
+  <si>
+    <t>Standard operating procedures for field implementation and data collection of on-farm trials with the tricot approach</t>
+  </si>
+  <si>
+    <t>Scientific name</t>
+  </si>
+  <si>
+    <t>Nome científico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All plots well are labelled using letters (sub-plot A, sub-plot B, and sub-plot C). Sub-plots should be established on the same planting date and follow the same dimensions and management practices. The three sub-plots should be located very close to ensure exposure to similar environmental and management conditions. </t>
+  </si>
+  <si>
+    <t>If sufficient land is available, farmers are encouraged to establish an additional sub-plot of their preferred or commonly grown local variety ("Local") using the same planting date, dimensions, and management practices. Although the Local sub-plot is not part of the core tricot design, it is included in the end-of-season evaluation, where participants are asked whether the local variety performed better or worse than options A, B, and C.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sub-plot size should follow recommendations from the Product Management Team (PMT) and be appropriate for the crop and farming system. Information on sub-plot dimensions should be recorded in the trial metadata. For `r cropname` the advised sub-plot size is `r plotdimension` which requires `r numberplants` per sub-plot. </t>
+  </si>
+  <si>
+    <t>O termo de consentimento informado fornece uma estrutura padronizada para garantir que todos os participantes estejam adequadamente informados antes de participar do experimento e dos questionários associados. O documento explica os objetivos da coleta de dados, os tipos de informações que serão coletadas e como esses dados poderão ser utilizados, incluindo para pesquisa e publicação. A participação é totalmente voluntária. Os participantes podem se recusar a responder qualquer pergunta ou retirar-se do estudo a qualquer momento, sem qualquer consequência negativa.</t>
+  </si>
+  <si>
+    <t>Caso haja área suficiente disponível, os agricultores são incentivados a estabelecer uma subparcela adicional com sua variedade local preferida ou mais comumente cultivada ("Local"), utilizando a mesma data de plantio, dimensões e práticas de manejo. Embora a subparcela Local não faça parte do desenho central do tricot, ela é incluída na avaliação final do ensaio, quando os participantes são questionados se a variedade local apresentou desempenho melhor ou pior do que as opções A, B e C.</t>
+  </si>
+  <si>
+    <t>O tamanho das subparcelas deve seguir as recomendações da Equipe de Gestão de Produto (PMT) e ser apropriado para a cultura e o sistema produtivo. As dimensões das subparcelas devem ser registradas nos metadados do ensaio. Para `r cropname`, o tamanho recomendado da subparcela é `r plotdimension`, exigindo `r numberplants` por subparcela.</t>
+  </si>
+  <si>
+    <t>Materiais e equipamentos</t>
+  </si>
+  <si>
+    <t>A coleta de dados em ensaios tricot pode ser realizada por meio de questionários digitais aplicados por técnicos de campo ou por fichas de observação preenchidas pelos participantes. Dependendo da abordagem de coleta de dados adotada, os seguintes materiais e equipamentos podem ser necessários.</t>
+  </si>
+  <si>
+    <t>**Coleta digital de dados (ODK):** i) Smartphone ou tablet Android com bateria suficiente; ii) Aplicativo ODK Collect instalado e configurado; iii) Conexão com a internet para download e envio dos formulários (quando disponível); iv) Power bank ou equipamento de carregamento para trabalho de campo; v) Listas de participantes e registros de alocação dos ensaios.</t>
+  </si>
+  <si>
+    <t>**Coleta de dados por fichas de observação:** i) Fichas de observação impressas; ii) Canetas ou lápis para os participantes; iii) Etiquetas identificando as opções A, B e C; iv) Listas de participantes e registros de alocação dos ensaios.</t>
+  </si>
+  <si>
+    <t>**Entrada e compilação de dados:** i) Computador com acesso à internet; ii) Acesso à plataforma ClimMob; iii) Formulários Enketo para entrada direta dos dados; ou iv) Planilhas Excel do ClimMob para entrada offline e posterior envio.</t>
+  </si>
+  <si>
+    <t>As equipes do projeto devem selecionar o método de coleta de dados mais adequado às condições locais, às preferências dos participantes e aos recursos disponíveis.</t>
+  </si>
+  <si>
+    <t>Observação do ensaio e coleta de dados</t>
+  </si>
+  <si>
+    <t>As fichas de observação devem conter perguntas comparativas simples que permitam aos participantes identificar a melhor e a pior opção para cada critério de avaliação. Os participantes devem ser incentivados a concentrar-se em um critério por vez ao realizar suas avaliações. As equipes do projeto são incentivadas a fornecer acompanhamento por meio de visitas de campo, chamadas telefônicas ou outros canais de comunicação para lembrar os participantes sobre as próximas observações, responder dúvidas e apoiar a coleta oportuna dos dados.</t>
+  </si>
+  <si>
+    <t>O registro dos participantes é realizado durante a distribuição dos kits do ensaio e deve ser concluído para todos os participantes antes do início de quaisquer atividades subsequentes de coleta de dados. Os kits devem ser distribuídos com antecedência suficiente em relação ao plantio para permitir que os participantes tenham tempo adequado para o preparo da área e o estabelecimento do ensaio. O objetivo do registro é vincular cada participante a um kit único do ensaio e coletar as informações mínimas necessárias para a gestão do ensaio e o acompanhamento dos participantes.</t>
+  </si>
+  <si>
+    <t>Registro de participantes</t>
+  </si>
+  <si>
+    <t>As atividades de registro devem ser tão breves e eficientes quanto possível, pois a distribuição dos kits geralmente é uma atividade intensa, durante a qual a equipe do projeto precisa distribuir materiais, explicar os procedimentos do ensaio, responder às dúvidas dos participantes e fornecer orientações para sua implementação. A conclusão do registro é obrigatória para a inclusão nas atividades subsequentes de coleta e análise de dados. Durante o registro, a equipe do projeto deve explicar os objetivos do ensaio, os procedimentos de estabelecimento das parcelas, o cronograma de observações e as responsabilidades dos participantes durante todo o período experimental.</t>
+  </si>
+  <si>
+    <t>Pesquisa socioeconômica de linha de base</t>
+  </si>
+  <si>
+    <t>A pesquisa socioeconômica de linha de base coleta informações sobre as características dos participantes, composição familiar, atividades agrícolas, práticas de manejo da cultura, sistemas de sementes, participação em mercados e acesso a serviços agrícolas. O objetivo desta pesquisa é identificar fatores socioeconômicos associados ao manejo de variedades e às preferências dos agricultores, além de apoiar a interpretação dos resultados do ensaio entre diferentes grupos de participantes.</t>
+  </si>
+  <si>
+    <t>Como a pesquisa socioeconômica é mais abrangente do que o formulário de registro dos participantes, ela não precisa ser aplicada no mesmo momento da distribuição dos kits do ensaio. A pesquisa pode ser realizada durante visitas de acompanhamento ou em qualquer outro momento adequado ao longo do período experimental. As equipes do projeto podem aplicar a pesquisa a diferentes grupos de participantes ao longo da execução do ensaio, de acordo com os recursos disponíveis e as restrições operacionais. Embora a realização da pesquisa seja recomendada para todos os participantes, as equipes podem priorizar uma amostra representativa quando os recursos forem limitados. Sempre que possível, a pesquisa deve ser concluída antes da análise final dos dados para permitir a integração das informações socioeconômicas com as observações e avaliações dos participantes.</t>
+  </si>
+  <si>
+    <t>Componentes do questionário</t>
+  </si>
+  <si>
+    <t>A estrutura de coleta de dados do tricot é composta por múltiplos componentes de questionários implementados ao longo da duração do ensaio. Esses componentes coletam informações complementares necessárias para a gestão do ensaio, acompanhamento dos participantes, caracterização das condições experimentais e avaliação do desempenho das tecnologias. A coleta de dados inicia-se com o registro dos participantes e o consentimento informado, seguida pelas observações realizadas nos diferentes estágios da cultura. Dependendo dos objetivos do projeto e dos recursos disponíveis, informações socioeconômicas adicionais podem ser coletadas de todos os participantes ou de uma amostra representativa.</t>
+  </si>
+  <si>
+    <t>Ao final do ensaio, os participantes realizam avaliações finais das tecnologias testadas, incluindo observações pós-colheita. As seções seguintes apresentam a lista completa de variáveis, perguntas e momentos de coleta de dados associados a este protocolo tricot. Este questionário está disponível no ClimMob como um modelo de projeto denominado `r templatename`.</t>
+  </si>
+  <si>
+    <r>
+      <t>Este documento apresenta uma visão abrangente dos dados que serão coletados durante ensaios participativos conduzidos em propriedades rurais utilizando a abordagem tricot e desenvolvidos na plataforma ClimMob (https://climmob.net</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>). O protocolo descreve os principais momentos de coleta de dados ao longo dos ensaios, incluindo as variáveis e características avaliadas em cada estágio de desenvolvimento da cultura. Os agricultores avaliam as variedades em seus ensaios on-farm e fornecem observações comparativas ao classificá-las com base em seu desempenho relativo durante o ciclo de crescimento e em características pós-colheita. Uma descrição mais detalhada das etapas necessárias para desenvolver um ensaio participativo utilizando a abordagem tricot está disponível em </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://learn.climmob.net.</t>
+    </r>
+  </si>
+  <si>
+    <t>Todas as parcelas são identificadas por letras (subparcela A, subparcela B e subparcela C). As subparcelas devem ser estabelecidas na mesma data de plantio e seguir as mesmas dimensões e práticas de manejo. As três subparcelas devem estar localizadas próximas umas das outras, de modo a garantir exposição a condições ambientais e de manejo semelhantes.</t>
+  </si>
+  <si>
+    <t>**Abrangência:** Este SOP descreve os procedimentos e padrões para a implementação de ensaios participativos descentralizados em propriedades rurais utilizando a abordagem tricot. O documento abrange o desenho experimental, a documentação, o monitoramento e a gestão de dados dos ensaios tricot. O SOP inclui orientações sobre configuração de questionários digitais, coleta de dados, padrões de metadados e procedimentos básicos de garantia da qualidade para apoiar a geração de dados FAIR. Este SOP foi desenvolvido para apoiar a implementação padronizada de ensaios tricot, permitindo ao mesmo tempo adaptações às culturas, sistemas produtivos, idiomas e contextos institucionais locais.</t>
+  </si>
+  <si>
+    <t>**Exclusões:** Este SOP não contempla orientações sobre seleção de genótipos, seleção de participantes, análises estatísticas avançadas, processos de tomada de decisão em programas de melhoramento, procedimentos laboratoriais, multiplicação de sementes ou protocolos de certificação. Procedimentos específicos relacionados a análises genômicas, modelagem climática, regulamentações para transporte de sementes ou fenotipagem laboratorial devem ser abordados em SOPs específicos, quando aplicável.</t>
+  </si>
+  <si>
+    <t>**Público-alvo:** Este SOP destina-se a melhoristas, agrônomos, profissionais de bancos de germoplasma, organizações não governamentais, organizações de agricultores, estudantes e pesquisadores envolvidos na implementação, coordenação e gestão de ensaios tricot e de experimentação participativa descentralizada.</t>
+  </si>
+  <si>
+    <t>O consentimento é obtido antes da coleta de dados para garantir transparência, práticas éticas de pesquisa e respeito aos direitos dos participantes. O fornecimento do consentimento informado é um pré-requisito para a inclusão em todas as atividades subsequentes do ensaio e dos questionários. Um modelo de termo de consentimento informado é apresentado como anexo deste SOP.</t>
+  </si>
+  <si>
+    <t>Os participantes observam as parcelas que lhes foram atribuídas durante todo o período do ensaio e registram suas observações em momentos predefinidos de coleta de dados (estágios de desenvolvimento da cultura). Os dados podem ser coletados diretamente por técnicos utilizando ODK em dispositivos Android ou registrados pelos participantes em fichas de observação e posteriormente digitalizados no ClimMob por meio de formulários Enketo ou planilhas Excel. Este SOP define os momentos de observação, alinhados aos estágios de desenvolvimento da cultura, que devem ser claramente comunicados aos participantes durante a distribuição dos kits do ensaio e ao longo de todo o período experimental.</t>
+  </si>
+  <si>
+    <t>Outros recursos e SOPs</t>
+  </si>
+  <si>
+    <t>A tabela a seguir apresenta orientações adicionais e SOPs que podem apoiar o planejamento, a implementação, a documentação e a análise de ensaios tricot.</t>
+  </si>
+  <si>
+    <t>Procedimentos operacionais padrão para iimplementação e coleta de dados em ensaios experimentais em fazendas com a abordagem tricot</t>
   </si>
 </sst>
 </file>
@@ -819,106 +929,106 @@
     </row>
     <row r="2" spans="1:5" ht="102" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>89</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="B10" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="B14" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -928,12 +1038,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB5FF5ED-AA91-F847-8546-368AFFC4F6A2}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.33203125" style="3" customWidth="1"/>
     <col min="2" max="2" width="49.83203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="43.6640625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="61.5" style="4" customWidth="1"/>
     <col min="4" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
@@ -968,15 +1078,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="251" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="238" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>80</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -987,40 +1097,40 @@
         <v>14</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="306" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="221" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="221" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="136" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="102" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>82</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -1031,168 +1141,293 @@
         <v>10</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="404" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="187" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="102" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>48</v>
+        <v>111</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="102" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="68" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="85" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="204" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="170" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="51" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+      <c r="C24" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="187" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B25" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="204" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="153" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="180" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
+      <c r="B28" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="289" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="372" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
+      <c r="C30" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="221" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
+      <c r="B31" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
+      <c r="B34" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="340" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>74</v>
+      <c r="C34" s="4" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -1232,24 +1467,24 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -1260,7 +1495,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -1271,7 +1506,7 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -1282,7 +1517,7 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -1293,7 +1528,7 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -1304,7 +1539,7 @@
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -1315,15 +1550,18 @@
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/data/base-text-sop.xlsx
+++ b/data/base-text-sop.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-protocols/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E366FB0-405C-0C45-9517-9E9AEF8688A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D453163F-6D80-3241-B308-7E73BC2F060D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="16700" xr2:uid="{CCA2DD50-73A2-AB48-A73E-30174A4C4548}"/>
+    <workbookView xWindow="980" yWindow="600" windowWidth="29740" windowHeight="16700" activeTab="1" xr2:uid="{CCA2DD50-73A2-AB48-A73E-30174A4C4548}"/>
   </bookViews>
   <sheets>
     <sheet name="title" sheetId="3" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="301">
   <si>
     <t>en</t>
   </si>
@@ -139,9 +139,6 @@
     <t>https://learn.climmob.net/preparation/budgeting</t>
   </si>
   <si>
-    <t>Check list for implementing on-farm trial</t>
-  </si>
-  <si>
     <t>https://learn.climmob.net/preparation/checklist</t>
   </si>
   <si>
@@ -331,9 +328,6 @@
     <t>Este documento também está disponível em</t>
   </si>
   <si>
-    <t>This document provides a comprehensive overview of the data to be collected during on-farm trials using the tricot approach and designed on ClimMob platform (https://climmob.net). The protocol outlines the key  data collection points throughout  the trials, including the variables and traits to be collected at each crop growth stage. Farmers evaluate varieties in their on-farm trials and provide comparative observations by ranking the varieties based on their relative performance throughout their growth and post-harvest qualities. A more in-depth overview of the steps required for developing a participatory on-farm trial using tricot is available here https://learn.climmob.net.</t>
-  </si>
-  <si>
     <t>Budget for a tricot trial</t>
   </si>
   <si>
@@ -388,9 +382,6 @@
     <t>If sufficient land is available, farmers are encouraged to establish an additional sub-plot of their preferred or commonly grown local variety ("Local") using the same planting date, dimensions, and management practices. Although the Local sub-plot is not part of the core tricot design, it is included in the end-of-season evaluation, where participants are asked whether the local variety performed better or worse than options A, B, and C.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sub-plot size should follow recommendations from the Product Management Team (PMT) and be appropriate for the crop and farming system. Information on sub-plot dimensions should be recorded in the trial metadata. For `r cropname` the advised sub-plot size is `r plotdimension` which requires `r numberplants` per sub-plot. </t>
-  </si>
-  <si>
     <t>O termo de consentimento informado fornece uma estrutura padronizada para garantir que todos os participantes estejam adequadamente informados antes de participar do experimento e dos questionários associados. O documento explica os objetivos da coleta de dados, os tipos de informações que serão coletadas e como esses dados poderão ser utilizados, incluindo para pesquisa e publicação. A participação é totalmente voluntária. Os participantes podem se recusar a responder qualquer pergunta ou retirar-se do estudo a qualquer momento, sem qualquer consequência negativa.</t>
   </si>
   <si>
@@ -451,8 +442,38 @@
     <t>Ao final do ensaio, os participantes realizam avaliações finais das tecnologias testadas, incluindo observações pós-colheita. As seções seguintes apresentam a lista completa de variáveis, perguntas e momentos de coleta de dados associados a este protocolo tricot. Este questionário está disponível no ClimMob como um modelo de projeto denominado `r templatename`.</t>
   </si>
   <si>
+    <t>Todas as parcelas são identificadas por letras (subparcela A, subparcela B e subparcela C). As subparcelas devem ser estabelecidas na mesma data de plantio e seguir as mesmas dimensões e práticas de manejo. As três subparcelas devem estar localizadas próximas umas das outras, de modo a garantir exposição a condições ambientais e de manejo semelhantes.</t>
+  </si>
+  <si>
+    <t>**Abrangência:** Este SOP descreve os procedimentos e padrões para a implementação de ensaios participativos descentralizados em propriedades rurais utilizando a abordagem tricot. O documento abrange o desenho experimental, a documentação, o monitoramento e a gestão de dados dos ensaios tricot. O SOP inclui orientações sobre configuração de questionários digitais, coleta de dados, padrões de metadados e procedimentos básicos de garantia da qualidade para apoiar a geração de dados FAIR. Este SOP foi desenvolvido para apoiar a implementação padronizada de ensaios tricot, permitindo ao mesmo tempo adaptações às culturas, sistemas produtivos, idiomas e contextos institucionais locais.</t>
+  </si>
+  <si>
+    <t>**Exclusões:** Este SOP não contempla orientações sobre seleção de genótipos, seleção de participantes, análises estatísticas avançadas, processos de tomada de decisão em programas de melhoramento, procedimentos laboratoriais, multiplicação de sementes ou protocolos de certificação. Procedimentos específicos relacionados a análises genômicas, modelagem climática, regulamentações para transporte de sementes ou fenotipagem laboratorial devem ser abordados em SOPs específicos, quando aplicável.</t>
+  </si>
+  <si>
+    <t>**Público-alvo:** Este SOP destina-se a melhoristas, agrônomos, profissionais de bancos de germoplasma, organizações não governamentais, organizações de agricultores, estudantes e pesquisadores envolvidos na implementação, coordenação e gestão de ensaios tricot e de experimentação participativa descentralizada.</t>
+  </si>
+  <si>
+    <t>O consentimento é obtido antes da coleta de dados para garantir transparência, práticas éticas de pesquisa e respeito aos direitos dos participantes. O fornecimento do consentimento informado é um pré-requisito para a inclusão em todas as atividades subsequentes do ensaio e dos questionários. Um modelo de termo de consentimento informado é apresentado como anexo deste SOP.</t>
+  </si>
+  <si>
+    <t>Os participantes observam as parcelas que lhes foram atribuídas durante todo o período do ensaio e registram suas observações em momentos predefinidos de coleta de dados (estágios de desenvolvimento da cultura). Os dados podem ser coletados diretamente por técnicos utilizando ODK em dispositivos Android ou registrados pelos participantes em fichas de observação e posteriormente digitalizados no ClimMob por meio de formulários Enketo ou planilhas Excel. Este SOP define os momentos de observação, alinhados aos estágios de desenvolvimento da cultura, que devem ser claramente comunicados aos participantes durante a distribuição dos kits do ensaio e ao longo de todo o período experimental.</t>
+  </si>
+  <si>
+    <t>Outros recursos e SOPs</t>
+  </si>
+  <si>
+    <t>A tabela a seguir apresenta orientações adicionais e SOPs que podem apoiar o planejamento, a implementação, a documentação e a análise de ensaios tricot.</t>
+  </si>
+  <si>
+    <t>Procedimentos operacionais padrão para iimplementação e coleta de dados em ensaios experimentais em fazendas com a abordagem tricot</t>
+  </si>
+  <si>
+    <t>This document provides a comprehensive overview of the data to be collected during a `r cropname` on-farm trial implemented using the tricot approach and designed on ClimMob platform (https://climmob.net). The protocol outlines the key  data collection points throughout  the trials, including the variables and traits to be collected at each crop growth stage. Farmers evaluate varieties in their on-farm trials and provide comparative observations by ranking the varieties based on their relative performance throughout their growth and post-harvest qualities. A more in-depth overview of the steps required for developing a participatory on-farm trial using tricot is available here https://learn.climmob.net.</t>
+  </si>
+  <si>
     <r>
-      <t>Este documento apresenta uma visão abrangente dos dados que serão coletados durante ensaios participativos conduzidos em propriedades rurais utilizando a abordagem tricot e desenvolvidos na plataforma ClimMob (https://climmob.net</t>
+      <t>Este documento apresenta uma visão abrangente dos dados que serão coletados durante ensaios participativos com `r cropname` conduzidos em propriedades rurais utilizando a abordagem tricot e desenvolvidos na plataforma ClimMob (https://climmob.net</t>
     </r>
     <r>
       <rPr>
@@ -474,38 +495,491 @@
     </r>
   </si>
   <si>
-    <t>Todas as parcelas são identificadas por letras (subparcela A, subparcela B e subparcela C). As subparcelas devem ser estabelecidas na mesma data de plantio e seguir as mesmas dimensões e práticas de manejo. As três subparcelas devem estar localizadas próximas umas das outras, de modo a garantir exposição a condições ambientais e de manejo semelhantes.</t>
-  </si>
-  <si>
-    <t>**Abrangência:** Este SOP descreve os procedimentos e padrões para a implementação de ensaios participativos descentralizados em propriedades rurais utilizando a abordagem tricot. O documento abrange o desenho experimental, a documentação, o monitoramento e a gestão de dados dos ensaios tricot. O SOP inclui orientações sobre configuração de questionários digitais, coleta de dados, padrões de metadados e procedimentos básicos de garantia da qualidade para apoiar a geração de dados FAIR. Este SOP foi desenvolvido para apoiar a implementação padronizada de ensaios tricot, permitindo ao mesmo tempo adaptações às culturas, sistemas produtivos, idiomas e contextos institucionais locais.</t>
-  </si>
-  <si>
-    <t>**Exclusões:** Este SOP não contempla orientações sobre seleção de genótipos, seleção de participantes, análises estatísticas avançadas, processos de tomada de decisão em programas de melhoramento, procedimentos laboratoriais, multiplicação de sementes ou protocolos de certificação. Procedimentos específicos relacionados a análises genômicas, modelagem climática, regulamentações para transporte de sementes ou fenotipagem laboratorial devem ser abordados em SOPs específicos, quando aplicável.</t>
-  </si>
-  <si>
-    <t>**Público-alvo:** Este SOP destina-se a melhoristas, agrônomos, profissionais de bancos de germoplasma, organizações não governamentais, organizações de agricultores, estudantes e pesquisadores envolvidos na implementação, coordenação e gestão de ensaios tricot e de experimentação participativa descentralizada.</t>
-  </si>
-  <si>
-    <t>O consentimento é obtido antes da coleta de dados para garantir transparência, práticas éticas de pesquisa e respeito aos direitos dos participantes. O fornecimento do consentimento informado é um pré-requisito para a inclusão em todas as atividades subsequentes do ensaio e dos questionários. Um modelo de termo de consentimento informado é apresentado como anexo deste SOP.</t>
-  </si>
-  <si>
-    <t>Os participantes observam as parcelas que lhes foram atribuídas durante todo o período do ensaio e registram suas observações em momentos predefinidos de coleta de dados (estágios de desenvolvimento da cultura). Os dados podem ser coletados diretamente por técnicos utilizando ODK em dispositivos Android ou registrados pelos participantes em fichas de observação e posteriormente digitalizados no ClimMob por meio de formulários Enketo ou planilhas Excel. Este SOP define os momentos de observação, alinhados aos estágios de desenvolvimento da cultura, que devem ser claramente comunicados aos participantes durante a distribuição dos kits do ensaio e ao longo de todo o período experimental.</t>
-  </si>
-  <si>
-    <t>Outros recursos e SOPs</t>
-  </si>
-  <si>
-    <t>A tabela a seguir apresenta orientações adicionais e SOPs que podem apoiar o planejamento, a implementação, a documentação e a análise de ensaios tricot.</t>
-  </si>
-  <si>
-    <t>Procedimentos operacionais padrão para iimplementação e coleta de dados em ensaios experimentais em fazendas com a abordagem tricot</t>
+    <t xml:space="preserve">Sub-plot size should follow recommendations from the Product Management Team (PMT) and be appropriate for the crop and farming system. Information on sub-plot dimensions should be recorded in the trial metadata. For `r cropname` the advised sub-plot size is `r plotdimension`, which requires `r numberplants` per sub-plot. </t>
+  </si>
+  <si>
+    <t>Ce document fournit une vue d’ensemble complète des données qui seront collectées dans le cadre d’un essai participatif en exploitation de `r cropname`, mis en œuvre selon l’approche tricot et conçu sur la plateforme ClimMob (https://climmob.net). Le protocole décrit les principaux points de collecte de données tout au long de l’essai, y compris les variables et caractéristiques à évaluer à chaque stade de développement de la culture. Les agriculteurs évaluent les variétés dans leurs essais en exploitation et fournissent des observations comparatives en classant les variétés selon leurs performances relatives tout au long de leur croissance et de leurs qualités post-récolte. Une présentation plus détaillée des étapes nécessaires à la mise en place d’un essai participatif utilisant l’approche tricot est disponible à l’adresse suivante : https://learn.climmob.net.</t>
+  </si>
+  <si>
+    <t>Portée</t>
+  </si>
+  <si>
+    <t>**Couverture :** Cette SOP décrit les procédures et les normes relatives à la mise en œuvre d’essais participatifs décentralisés en exploitation utilisant l’approche tricot. Elle couvre le dispositif expérimental, la documentation, le suivi et la gestion des données des essais tricot. La SOP comprend des recommandations concernant la configuration des enquêtes numériques, la collecte de données, les normes de métadonnées et les procédures de base d’assurance qualité afin de soutenir la production de données FAIR. Cette SOP vise à soutenir une mise en œuvre harmonisée des essais tricot tout en permettant une adaptation aux cultures, systèmes agricoles, langues et contextes institutionnels locaux.</t>
+  </si>
+  <si>
+    <t>**Exclusions :** Cette SOP ne couvre pas la sélection des génotypes, la sélection des participants, les analyses statistiques avancées, les processus de prise de décision en amélioration variétale, les procédures d’analyse en laboratoire, la multiplication et la certification des semences. Les procédures spécifiques liées aux analyses génomiques, à la modélisation climatique, aux réglementations relatives au transport des semences ou au phénotypage en laboratoire doivent être traitées dans des SOP distinctes lorsque cela est pertinent.</t>
+  </si>
+  <si>
+    <t>**Public cible :** Cette SOP s’adresse aux sélectionneurs, agronomes, personnels des banques de gènes, ONG, organisations de producteurs, étudiants et chercheurs impliqués dans la mise en œuvre, la coordination et la gestion des essais tricot ainsi que de l’expérimentation participative décentralisée.</t>
+  </si>
+  <si>
+    <t>Consentement éclairé</t>
+  </si>
+  <si>
+    <t>Le formulaire de consentement éclairé fournit un cadre normalisé garantissant que tous les participants sont correctement informés avant de prendre part à l’essai et aux enquêtes associées. Il explique l’objectif de la collecte de données, les types d’informations qui seront recueillies et l’utilisation qui pourra être faite de ces données, notamment à des fins de recherche et de publication. La participation est entièrement volontaire. Les participants peuvent refuser de répondre à une question ou se retirer de l’étude à tout moment sans conséquence négative.</t>
+  </si>
+  <si>
+    <t>Le consentement est obtenu avant toute collecte de données afin de garantir la transparence, le respect de l’éthique de la recherche et des droits des participants. Le consentement éclairé est une condition préalable à l’inclusion dans toutes les activités ultérieures de l’essai et des enquêtes. Un modèle de formulaire de consentement éclairé est annexé à cette SOP.</t>
+  </si>
+  <si>
+    <t>Plan expérimental</t>
+  </si>
+  <si>
+    <t>Toutes les parcelles sont identifiées par des lettres (sous-parcelle A, sous-parcelle B et sous-parcelle C). Les sous-parcelles doivent être établies à la même date de plantation et suivre les mêmes dimensions et pratiques de gestion. Les trois sous-parcelles doivent être situées très près les unes des autres afin de garantir une exposition à des conditions environnementales et de gestion similaires.</t>
+  </si>
+  <si>
+    <t>Si des terres suffisantes sont disponibles, les agriculteurs sont encouragés à établir une sous-parcelle supplémentaire avec leur variété locale préférée ou la plus couramment cultivée (« Local »), en utilisant la même date de plantation, les mêmes dimensions et les mêmes pratiques de gestion. Bien que la sous-parcelle Local ne fasse pas partie du dispositif central du tricot, elle est incluse dans l’évaluation de fin de saison, au cours de laquelle les participants indiquent si la variété locale a obtenu de meilleures ou de moins bonnes performances que les options A, B et C.</t>
+  </si>
+  <si>
+    <t>La taille des sous-parcelles doit suivre les recommandations de l’Équipe de Gestion du Produit (PMT) et être adaptée à la culture et au système de production. Les dimensions des sous-parcelles doivent être enregistrées dans les métadonnées de l’essai. Pour `r cropname`, la taille recommandée des sous-parcelles est de `r plotdimension`, ce qui nécessite `r numberplants` par sous-parcelle.</t>
+  </si>
+  <si>
+    <t>Matériel et équipements</t>
+  </si>
+  <si>
+    <t>La collecte de données dans les essais tricot peut être réalisée soit au moyen d’enquêtes numériques administrées par le personnel de terrain, soit à l’aide de fiches d’observation remplies par les participants. Selon l’approche de collecte de données retenue, les matériels et équipements suivants peuvent être nécessaires.</t>
+  </si>
+  <si>
+    <t>**Collecte numérique des données (ODK) :** i) Smartphone ou tablette Android disposant d’une autonomie suffisante ; ii) Application ODK Collect installée et configurée ; iii) Connexion Internet pour télécharger et soumettre les formulaires (lorsqu’elle est disponible) ; iv) Batterie externe ou équipement de recharge pour le travail de terrain ; v) Listes des participants et registres d’attribution des essais.</t>
+  </si>
+  <si>
+    <t>**Collecte de données à l’aide de fiches d’observation :** i) Fiches d’observation imprimées ; ii) Stylos ou crayons pour les participants ; iii) Étiquettes identifiant les options A, B et C ; iv) Listes des participants et registres d’attribution des essais.</t>
+  </si>
+  <si>
+    <t>**Saisie et compilation des données :** i) Ordinateur avec accès à Internet ; ii) Accès à la plateforme ClimMob ; iii) Formulaires web Enketo pour la saisie directe des données ; ou iv) Modèles Excel ClimMob pour la saisie hors ligne et le téléversement ultérieur.</t>
+  </si>
+  <si>
+    <t>Les équipes du projet doivent sélectionner la méthode de collecte de données la plus adaptée aux conditions locales, aux préférences des participants et aux ressources disponibles.</t>
+  </si>
+  <si>
+    <t>Observation et collecte des données</t>
+  </si>
+  <si>
+    <t>Les participants observent les parcelles qui leur ont été attribuées tout au long de l’essai et enregistrent leurs observations aux moments prédéfinis de collecte des données (stades de développement de la culture). Les données peuvent être collectées directement par des techniciens de terrain à l’aide d’ODK sur des appareils Android ou enregistrées par les participants sur des fiches d’observation puis numérisées dans ClimMob à l’aide de formulaires Enketo ou de modèles Excel. Cette SOP définit les moments d’observation, alignés sur les stades de développement de la culture, qui doivent être clairement communiqués aux participants lors de la distribution du kit d’essai et tout au long de la période de l’essai.</t>
+  </si>
+  <si>
+    <t>Les fiches d’observation doivent contenir des questions comparatives simples permettant aux participants d’identifier la meilleure et la moins bonne option pour chaque critère d’évaluation. Les participants doivent être encouragés à se concentrer sur un seul critère à la fois lors de leurs évaluations. Les équipes du projet sont encouragées à assurer un suivi par des visites de terrain, des appels téléphoniques ou d’autres moyens de communication afin de rappeler les prochaines observations, répondre aux questions et soutenir la collecte des données en temps opportun.</t>
+  </si>
+  <si>
+    <t>Enregistrement des participants</t>
+  </si>
+  <si>
+    <t>L’enregistrement des participants est réalisé lors de la distribution des kits d’essai et doit être complété pour tous les participants avant que toute activité ultérieure de collecte de données puisse avoir lieu. Les kits d’essai doivent être distribués suffisamment avant la plantation afin de permettre aux participants de disposer du temps nécessaire pour préparer la parcelle et établir l’essai. L’objectif de l’enregistrement est d’associer chaque participant à un kit d’essai unique et de collecter les informations minimales nécessaires à la gestion de l’essai et au suivi des participants.</t>
+  </si>
+  <si>
+    <t>Les activités d’enregistrement doivent rester aussi brèves et efficaces que possible, car la distribution des kits constitue souvent une activité intense au cours de laquelle le personnel du projet doit distribuer le matériel de l’essai, expliquer les procédures, répondre aux questions des participants et fournir des conseils pour la mise en œuvre. L’enregistrement des participants est obligatoire pour être inclus dans les activités ultérieures de collecte de données et dans les analyses. Lors de l’enregistrement, le personnel du projet doit expliquer les objectifs de l’essai, les procédures de mise en place des parcelles, le calendrier des observations et les responsabilités des participants pendant toute la durée de l’essai.</t>
+  </si>
+  <si>
+    <t>Enquête socio-économique de référence</t>
+  </si>
+  <si>
+    <t>L’enquête socio-économique de référence collecte des informations sur les caractéristiques des participants, la composition du ménage, les activités agricoles, les pratiques de gestion des cultures, les systèmes semenciers, la participation aux marchés et l’accès aux services agricoles. L’objectif de cette enquête est d’identifier les facteurs socio-économiques associés à la gestion des variétés et aux préférences des agriculteurs, ainsi que de soutenir l’interprétation des résultats des essais entre différents groupes de participants.</t>
+  </si>
+  <si>
+    <t>Comme l’enquête socio-économique est plus complète que le formulaire d’enregistrement des participants, elle n’a pas besoin d’être administrée au moment de la distribution des kits d’essai. L’enquête peut être réalisée lors des visites de suivi ou à tout autre moment approprié pendant la période de l’essai. Les équipes du projet peuvent administrer l’enquête à différents groupes de participants tout au long de l’essai en fonction des ressources disponibles et des contraintes opérationnelles. Bien qu’il soit recommandé que tous les participants répondent à l’enquête socio-économique, les équipes du projet peuvent privilégier un sous-échantillon représentatif lorsque les ressources sont limitées. Dans la mesure du possible, l’enquête doit être complétée avant l’analyse finale des données afin de permettre l’intégration des informations socio-économiques avec les observations et les évaluations des participants.</t>
+  </si>
+  <si>
+    <t>Composantes de l’enquête</t>
+  </si>
+  <si>
+    <t>Le cadre de collecte de données tricot est composé de plusieurs composantes d’enquête mises en œuvre tout au long de l’essai. Ces composantes collectent des informations complémentaires nécessaires à la gestion de l’essai, au suivi des participants, à la caractérisation des conditions de l’essai et à l’évaluation des performances des technologies. La collecte de données commence par l’enregistrement des participants et le consentement éclairé, suivis par les observations réalisées aux différents stades de développement de la culture. Selon les objectifs du projet et les ressources disponibles, des informations socio-économiques supplémentaires peuvent être collectées auprès de tous les participants ou d’un sous-échantillon représentatif.</t>
+  </si>
+  <si>
+    <t>À la fin de l’essai, les participants réalisent une évaluation finale des technologies testées, y compris les observations post-récolte. Les sections suivantes présentent la liste complète des variables, des questions et des moments de collecte de données associés à ce protocole tricot. Cette enquête est disponible dans ClimMob sous la forme d’un modèle de projet nommé `r templatename`.</t>
+  </si>
+  <si>
+    <t>Autres ressources et SOPs</t>
+  </si>
+  <si>
+    <t>Le tableau suivant présente des ressources complémentaires et des SOPs pouvant appuyer la planification, la mise en œuvre, la documentation et l’analyse des essais tricot.</t>
+  </si>
+  <si>
+    <t>Introducción</t>
+  </si>
+  <si>
+    <t>Este documento proporciona una visión general completa de los datos que se recopilarán durante un ensayo participativo en finca de `r cropname`, implementado mediante el enfoque tricot y diseñado en la plataforma ClimMob (https://climmob.net). El protocolo describe los principales puntos de recolección de datos a lo largo del ensayo, incluyendo las variables y características que se recopilarán en cada etapa de desarrollo del cultivo. Los agricultores evalúan las variedades en sus ensayos en finca y proporcionan observaciones comparativas clasificando las variedades según su desempeño relativo durante su crecimiento y sus cualidades poscosecha. Una descripción más detallada de los pasos necesarios para desarrollar un ensayo participativo en finca utilizando el enfoque tricot está disponible en https://learn.climmob.net.</t>
+  </si>
+  <si>
+    <t>Alcance</t>
+  </si>
+  <si>
+    <t>**Cobertura:** Este SOP describe los procedimientos y estándares para implementar ensayos participativos descentralizados en finca utilizando el enfoque tricot. Incluye el diseño de evaluación, la documentación, el monitoreo y la gestión de datos de los ensayos tricot. El SOP proporciona orientación sobre la configuración de encuestas digitales, la recolección de datos, los estándares de metadatos y los procedimientos básicos de aseguramiento de la calidad para apoyar la generación de datos FAIR. Este SOP tiene como objetivo apoyar una implementación estandarizada de los ensayos tricot, permitiendo al mismo tiempo su adaptación a cultivos, sistemas agrícolas, idiomas y contextos institucionales locales.</t>
+  </si>
+  <si>
+    <t>**Exclusiones:** Este SOP no cubre la selección de genotipos, la selección de participantes, los análisis estadísticos avanzados, los procesos de toma de decisiones en mejoramiento genético, los procedimientos de análisis de laboratorio, ni los protocolos de multiplicación y certificación de semillas. Los procedimientos específicos relacionados con análisis genómicos, modelación climática, regulaciones para el transporte de semillas o fenotipado de laboratorio deben abordarse en SOPs separados cuando corresponda.</t>
+  </si>
+  <si>
+    <t>**Público objetivo:** Este SOP está dirigido a mejoradores, agrónomos, personal de bancos de germoplasma, organizaciones no gubernamentales, organizaciones de agricultores, estudiantes e investigadores involucrados en la implementación, coordinación y gestión de ensayos tricot y de experimentación participativa descentralizada.</t>
+  </si>
+  <si>
+    <t>Consentimiento informado</t>
+  </si>
+  <si>
+    <t>El formulario de consentimiento informado proporciona un marco estandarizado para garantizar que todos los participantes estén adecuadamente informados antes de participar en el experimento y en las encuestas asociadas. Explica el propósito de la recolección de datos, los tipos de información que se recopilarán y cómo podrán utilizarse estos datos, incluyendo fines de investigación y publicación. La participación es completamente voluntaria. Los participantes pueden negarse a responder cualquier pregunta o retirarse del estudio en cualquier momento, sin ninguna consecuencia negativa.</t>
+  </si>
+  <si>
+    <t>El consentimiento se obtiene antes de la recolección de datos para garantizar la transparencia, las buenas prácticas éticas de investigación y el respeto por los derechos de los participantes. Proporcionar el consentimiento informado es un requisito previo para la inclusión en todas las actividades posteriores del ensayo y las encuestas. Se adjunta a este SOP un modelo de consentimiento informado.</t>
+  </si>
+  <si>
+    <t>Diseño experimental</t>
+  </si>
+  <si>
+    <t>Todas las parcelas están identificadas mediante letras (subparcela A, subparcela B y subparcela C). Las subparcelas deben establecerse en la misma fecha de siembra y seguir las mismas dimensiones y prácticas de manejo. Las tres subparcelas deben ubicarse muy cerca unas de otras para garantizar la exposición a condiciones ambientales y de manejo similares.</t>
+  </si>
+  <si>
+    <t>Si se dispone de suficiente terreno, se recomienda que los agricultores establezcan una subparcela adicional con su variedad local preferida o más comúnmente cultivada ("Local"), utilizando la misma fecha de siembra, dimensiones y prácticas de manejo. Aunque la subparcela Local no forma parte del diseño central de tricot, se incluye en la evaluación de final de temporada, donde se solicita a los participantes indicar si la variedad local tuvo un desempeño mejor o peor que las opciones A, B y C.</t>
+  </si>
+  <si>
+    <t>El tamaño de las subparcelas debe seguir las recomendaciones del Equipo de Gestión del Producto (PMT) y ser apropiado para el cultivo y el sistema agrícola. La información sobre las dimensiones de las subparcelas debe registrarse en los metadatos del ensayo. Para `r cropname`, el tamaño recomendado de la subparcela es `r plotdimension`, lo que requiere `r numberplants` por subparcela.</t>
+  </si>
+  <si>
+    <t>Materiales y equipos</t>
+  </si>
+  <si>
+    <t>La recolección de datos en los ensayos tricot puede realizarse mediante encuestas digitales administradas por el personal de campo o mediante tarjetas de observación completadas por los participantes. Dependiendo del enfoque de recolección de datos seleccionado, pueden requerirse los siguientes materiales y equipos.</t>
+  </si>
+  <si>
+    <t>**Recolección digital de datos (ODK):** i) Teléfono inteligente o tableta Android con suficiente capacidad de batería; ii) Aplicación ODK Collect instalada y configurada; iii) Conexión a Internet para descargar y enviar formularios (cuando esté disponible); iv) Batería externa o equipo de carga para el trabajo de campo; v) Listas de participantes y registros de asignación de ensayos.</t>
+  </si>
+  <si>
+    <t>**Recolección de datos mediante tarjetas de observación:** i) Tarjetas de observación impresas; ii) Bolígrafos o lápices para los participantes; iii) Etiquetas de ensayo identificando las opciones A, B y C; iv) Listas de participantes y registros de asignación de ensayos.</t>
+  </si>
+  <si>
+    <t>**Ingreso y compilación de datos:** i) Computadora con acceso a Internet; ii) Acceso a la plataforma ClimMob; iii) Formularios web Enketo para el ingreso directo de datos; o iv) Plantillas Excel de ClimMob para el ingreso de datos fuera de línea y su posterior carga.</t>
+  </si>
+  <si>
+    <t>Los equipos del proyecto deben seleccionar el método de recolección de datos más adecuado según las condiciones locales, las preferencias de los participantes y los recursos disponibles.</t>
+  </si>
+  <si>
+    <t>Observación del ensayo y recolección de datos</t>
+  </si>
+  <si>
+    <t>Los participantes observan las parcelas que les fueron asignadas durante toda la duración del ensayo y registran sus observaciones en momentos predefinidos de recolección de datos (etapas de desarrollo del cultivo). Los datos pueden ser recopilados directamente por técnicos de campo utilizando ODK en dispositivos Android o registrados por los participantes en tarjetas de observación y posteriormente digitalizados en ClimMob mediante formularios Enketo o plantillas Excel. Este SOP define los momentos de observación, los cuales están alineados con las etapas de desarrollo del cultivo y deben comunicarse claramente a los participantes durante la distribución del paquete del ensayo y a lo largo de todo el período de implementación.</t>
+  </si>
+  <si>
+    <t>Las tarjetas de observación deben contener preguntas comparativas simples que permitan a los participantes identificar la mejor y la peor opción para cada criterio de evaluación. Se debe alentar a los participantes a concentrarse en un criterio a la vez al realizar sus evaluaciones. Se recomienda que los equipos del proyecto proporcionen acompañamiento mediante visitas de campo, llamadas telefónicas u otros canales de comunicación para recordar a los participantes las próximas observaciones, responder preguntas y apoyar una recolección de datos oportuna.</t>
+  </si>
+  <si>
+    <t>El registro de participantes se realiza durante la distribución de los paquetes del ensayo y debe completarse para todos los participantes antes de que pueda llevarse a cabo cualquier actividad posterior de recolección de datos. Los paquetes del ensayo deben distribuirse con suficiente anticipación a la siembra para permitir que los participantes dispongan del tiempo necesario para la preparación del terreno y el establecimiento del ensayo. El propósito del registro es vincular a cada participante con un paquete único del ensayo y recopilar la información mínima necesaria para la gestión del ensayo y el seguimiento de los participantes.</t>
+  </si>
+  <si>
+    <t>Las actividades de registro deben ser lo más breves y eficientes posible, ya que la distribución de paquetes suele ser una actividad intensa durante la cual el personal del proyecto debe distribuir materiales, explicar los procedimientos del ensayo, responder preguntas y proporcionar orientación para su implementación. La finalización del registro es obligatoria para la inclusión en las actividades posteriores de recolección y análisis de datos. Durante el registro, el personal del proyecto debe explicar los objetivos del ensayo, los procedimientos para el establecimiento de las parcelas, el calendario de observaciones y las responsabilidades de los participantes durante toda la duración del ensayo.</t>
+  </si>
+  <si>
+    <t>Encuesta socioeconómica de línea base</t>
+  </si>
+  <si>
+    <t>La encuesta socioeconómica de línea base recopila información sobre las características de los participantes, la composición del hogar, las actividades agrícolas, las prácticas de manejo del cultivo, los sistemas de semillas, la participación en los mercados y el acceso a servicios agrícolas. El propósito de esta encuesta es identificar factores socioeconómicos asociados con el manejo de variedades y las preferencias de los agricultores, así como apoyar la interpretación de los resultados del ensayo entre diferentes grupos de participantes.</t>
+  </si>
+  <si>
+    <t>Dado que la encuesta socioeconómica es más amplia que el formulario de registro de participantes, no es necesario aplicarla al mismo tiempo que la distribución de los paquetes del ensayo. La encuesta puede realizarse durante visitas de seguimiento o en cualquier otro momento apropiado durante el período del ensayo. Los equipos del proyecto pueden administrar la encuesta a diferentes grupos de participantes a lo largo de la duración del ensayo, de acuerdo con los recursos disponibles y las limitaciones operativas. Aunque se recomienda que todos los participantes completen la encuesta socioeconómica, los equipos del proyecto pueden priorizar una muestra representativa cuando los recursos sean limitados. Siempre que sea posible, la encuesta debe completarse antes del análisis final de los datos para permitir la integración de la información socioeconómica con las observaciones y evaluaciones de los participantes.</t>
+  </si>
+  <si>
+    <t>Componentes de la encuesta</t>
+  </si>
+  <si>
+    <t>El marco de recolección de datos de tricot está compuesto por múltiples componentes de encuesta implementados a lo largo de la duración del ensayo. Estos componentes recopilan información complementaria necesaria para la gestión del ensayo, el seguimiento de los participantes, la caracterización de las condiciones del ensayo y la evaluación del desempeño de las tecnologías. La recolección de datos comienza con el registro de participantes y el consentimiento informado, seguida de observaciones realizadas en las distintas etapas de desarrollo del cultivo. Dependiendo de los objetivos del proyecto y de los recursos disponibles, puede recopilarse información socioeconómica adicional de todos los participantes o de una muestra representativa.</t>
+  </si>
+  <si>
+    <t>Al final del ensayo, los participantes realizan evaluaciones finales de las tecnologías evaluadas, incluidas las observaciones poscosecha. Las siguientes secciones presentan la lista completa de variables, preguntas y momentos de recolección de datos asociados con este protocolo tricot. Esta encuesta está disponible en ClimMob como una plantilla de proyecto denominada `r templatename`.</t>
+  </si>
+  <si>
+    <t>Otros recursos y SOPs</t>
+  </si>
+  <si>
+    <t>La siguiente tabla proporciona orientación adicional y SOPs que pueden apoyar la planificación, implementación, documentación y análisis de ensayos tricot.</t>
+  </si>
+  <si>
+    <t>Utangulizi</t>
+  </si>
+  <si>
+    <t>Hati hii inatoa muhtasari wa kina wa data zitakazokusanywa wakati wa jaribio la shambani la `r cropname` linalotekelezwa kwa kutumia mbinu ya tricot na kubuniwa kwenye jukwaa la ClimMob (https://climmob.net). Itifaki hii inaeleza hatua kuu za ukusanyaji wa data katika kipindi chote cha jaribio, ikijumuisha vigezo na sifa zitakazokusanywa katika kila hatua ya ukuaji wa zao. Wakulima hutathmini aina mbalimbali katika majaribio yao ya shambani na kutoa tathmini za kulinganisha kwa kupanga aina kulingana na utendaji wao wakati wa ukuaji na sifa za baada ya mavuno. Maelezo ya kina zaidi kuhusu hatua zinazohitajika kuandaa jaribio shirikishi la shambani kwa kutumia mbinu ya tricot yanapatikana katika https://learn.climmob.net.</t>
+  </si>
+  <si>
+    <t>Wigo</t>
+  </si>
+  <si>
+    <t>**Yanayohusika:** SOP hii inaeleza taratibu na viwango vya kutekeleza majaribio shirikishi ya shambani yaliyogatuliwa kwa kutumia mbinu ya tricot. Inajumuisha muundo wa tathmini, nyaraka, ufuatiliaji na usimamizi wa data za majaribio ya tricot. SOP hii inatoa mwongozo kuhusu usanidi wa dodoso za kidijitali, ukusanyaji wa data, viwango vya metadata na taratibu za msingi za uhakikisho wa ubora ili kusaidia uzalishaji wa data za FAIR. SOP hii imekusudiwa kusaidia utekelezaji wa majaribio ya tricot kwa njia iliyo sanifu huku ikiruhusu marekebisho kulingana na zao, mfumo wa uzalishaji, lugha na mazingira ya taasisi husika.</t>
+  </si>
+  <si>
+    <t>**Visivyohusika:** SOP hii haijumuishi mwongozo kuhusu uchaguzi wa jenotipu, uchaguzi wa washiriki, uchambuzi wa hali ya juu wa takwimu, michakato ya maamuzi katika uboreshaji wa mazao, taratibu za uchambuzi wa maabara, uzalishaji wa mbegu au taratibu za uthibitishaji wa mbegu. Taratibu maalum zinazohusiana na uchambuzi wa jenomu, utabiri wa hali ya hewa, kanuni za usafirishaji wa mbegu au tathmini za maabara zinapaswa kushughulikiwa katika SOP tofauti pale inapofaa.</t>
+  </si>
+  <si>
+    <t>**Walengwa:** SOP hii imekusudiwa kwa watafiti wa uboreshaji wa mazao, wataalamu wa kilimo, wahifadhi wa benki za jeni, mashirika yasiyo ya kiserikali, mashirika ya wakulima, wanafunzi na watafiti wanaohusika katika utekelezaji, uratibu na usimamizi wa majaribio ya tricot na majaribio shirikishi yaliyogatuliwa.</t>
+  </si>
+  <si>
+    <t>Ridhaa yenye ufahamu</t>
+  </si>
+  <si>
+    <t>Fomu ya ridhaa yenye ufahamu inatoa mfumo wa kawaida wa kuhakikisha kwamba washiriki wote wamepewa taarifa za kutosha kabla ya kushiriki katika jaribio na dodoso zinazohusiana nalo. Inaeleza madhumuni ya ukusanyaji wa data, aina za taarifa zitakazokusanywa na jinsi data hizo zitakavyoweza kutumika, ikiwa ni pamoja na matumizi ya utafiti na uchapishaji wa matokeo. Ushiriki ni wa hiari kabisa. Washiriki wanaweza kukataa kujibu swali lolote au kujiondoa katika utafiti wakati wowote bila madhara yoyote.</t>
+  </si>
+  <si>
+    <t>Ridhaa hukusanywa kabla ya ukusanyaji wa data ili kuhakikisha uwazi, maadili ya utafiti na heshima kwa haki za washiriki. Kutoa ridhaa yenye ufahamu ni sharti la kushiriki katika shughuli zote zinazofuata za jaribio na dodoso. Mfano wa fomu ya ridhaa yenye ufahamu umeambatishwa katika SOP hii.</t>
+  </si>
+  <si>
+    <t>Muundo wa jaribio</t>
+  </si>
+  <si>
+    <t>Maeneo yote ya majaribio hupewa alama za herufi (eneo dogo A, eneo dogo B na eneo dogo C). Maeneo haya madogo yanapaswa kupandwa katika tarehe moja na kufuata vipimo na mbinu sawa za usimamizi wa mazao. Maeneo hayo yanapaswa kuwa karibu ili kuhakikisha yanakabiliwa na mazingira na usimamizi unaofanana.</t>
+  </si>
+  <si>
+    <t>Iwapo kuna ardhi ya kutosha, wakulima wanahimizwa kuanzisha eneo dogo la ziada lenye aina yao ya kawaida au wanayoipendelea (“Local”), kwa kutumia tarehe ileile ya kupanda, vipimo vilevile na usimamizi unaofanana. Ingawa eneo la Local si sehemu ya msingi ya muundo wa tricot, linajumuishwa katika tathmini ya mwisho wa msimu ambapo washiriki huulizwa kama aina ya Local ilifanya vizuri zaidi au vibaya zaidi kuliko chaguo A, B na C.</t>
+  </si>
+  <si>
+    <t>Ukubwa wa eneo dogo unapaswa kufuata mapendekezo ya Timu ya Usimamizi wa Bidhaa (PMT) na kuwa unaofaa kwa zao na mfumo wa uzalishaji. Taarifa kuhusu vipimo vya eneo dogo zinapaswa kurekodiwa katika metadata za jaribio. Kwa `r cropname`, ukubwa unaopendekezwa wa eneo dogo ni `r plotdimension`, unaohitaji `r numberplants` kwa kila eneo dogo.</t>
+  </si>
+  <si>
+    <t>Vifaa na nyenzo</t>
+  </si>
+  <si>
+    <t>Ukusanyaji wa data katika majaribio ya tricot unaweza kufanyika kwa kutumia dodoso za kidijitali zinazosimamiwa na watendaji wa uwanjani au kwa kutumia kadi za uchunguzi zinazojazwa na washiriki. Kulingana na mbinu ya ukusanyaji wa data iliyochaguliwa, vifaa vifuatavyo vinaweza kuhitajika.</t>
+  </si>
+  <si>
+    <t>**Ukusanyaji wa data kwa njia ya kidijitali (ODK):** i) Simu janja au kompyuta kibao ya Android yenye uwezo wa kutosha wa betri; ii) Programu ya ODK Collect iliyosakinishwa na kusanidiwa; iii) Muunganisho wa intaneti kwa kupakua na kutuma fomu (pale unapopatikana); iv) Betri ya ziada au vifaa vya kuchaji kwa kazi za uwanjani; v) Orodha za washiriki na kumbukumbu za ugawaji wa majaribio.</t>
+  </si>
+  <si>
+    <t>**Ukusanyaji wa data kwa kutumia kadi za uchunguzi:** i) Kadi za uchunguzi zilizochapishwa; ii) Kalamu au penseli kwa washiriki; iii) Lebo za kutambua chaguo A, B na C; iv) Orodha za washiriki na kumbukumbu za ugawaji wa majaribio.</t>
+  </si>
+  <si>
+    <t>**Uingizaji na uandaaji wa data:** i) Kompyuta yenye muunganisho wa intaneti; ii) Upatikanaji wa jukwaa la ClimMob; iii) Fomu za Enketo kwa ajili ya uingizaji wa data moja kwa moja; au iv) Faili za Excel za ClimMob kwa ajili ya uingizaji wa data nje ya mtandao na upakiaji wa baadaye.</t>
+  </si>
+  <si>
+    <t>Timu za mradi zinapaswa kuchagua mbinu ya ukusanyaji wa data inayofaa zaidi kulingana na mazingira ya eneo husika, mapendeleo ya washiriki na rasilimali zilizopo.</t>
+  </si>
+  <si>
+    <t>Ufuatiliaji wa jaribio na ukusanyaji wa data</t>
+  </si>
+  <si>
+    <t>Washiriki hufuatilia maeneo yao ya majaribio waliyopewa katika kipindi chote cha jaribio na kurekodi uchunguzi wao katika vipindi vilivyopangwa vya ukusanyaji wa data (hatua za ukuaji wa zao). Data inaweza kukusanywa moja kwa moja na mafundi wa shambani kwa kutumia ODK kwenye vifaa vya Android au kurekodiwa na washiriki kwenye kadi za uchunguzi na baadaye kuingizwa katika ClimMob kwa kutumia fomu za Enketo au faili za Excel. SOP hii inaeleza vipindi vya uchunguzi vinavyolingana na hatua za ukuaji wa zao na vinapaswa kuelezwa kwa uwazi kwa washiriki wakati wa ugawaji wa kifurushi cha jaribio na katika kipindi chote cha utekelezaji wa jaribio.</t>
+  </si>
+  <si>
+    <t>Kadi za uchunguzi zinapaswa kuwa na maswali rahisi ya kulinganisha yanayowawezesha washiriki kutambua chaguo bora zaidi na chaguo dhaifu zaidi kwa kila kigezo cha tathmini. Washiriki wanapaswa kuhimizwa kuzingatia kigezo kimoja kwa wakati wanapofanya tathmini zao. Timu za mradi zinahimizwa kutoa msaada wa ufuatiliaji kupitia ziara za shambani, simu au njia nyingine za mawasiliano ili kuwakumbusha washiriki kuhusu uchunguzi unaofuata, kujibu maswali yao na kusaidia ukusanyaji wa data kwa wakati.</t>
+  </si>
+  <si>
+    <t>Usajili wa washiriki</t>
+  </si>
+  <si>
+    <t>Usajili wa washiriki hufanyika wakati wa ugawaji wa vifurushi vya majaribio na unapaswa kukamilishwa kwa washiriki wote kabla ya shughuli zozote za baadaye za ukusanyaji wa data kuanza. Vifurushi vya majaribio vinapaswa kusambazwa mapema vya kutosha kabla ya kupanda ili kuwapa washiriki muda wa kuandaa shamba na kuanzisha jaribio. Madhumuni ya usajili ni kumhusisha kila mshiriki na kifurushi cha kipekee cha jaribio na kukusanya taarifa za msingi zinazohitajika kwa usimamizi wa jaribio na ufuatiliaji wa washiriki.</t>
+  </si>
+  <si>
+    <t>Shughuli za usajili zinapaswa kuwa fupi na zenye ufanisi kadri inavyowezekana, kwa kuwa ugawaji wa vifurushi mara nyingi huwa shughuli yenye shughuli nyingi ambapo watendaji wa mradi wanahitaji kusambaza vifaa vya jaribio, kueleza taratibu za utekelezaji, kujibu maswali ya washiriki na kutoa maelekezo ya utekelezaji. Kukamilika kwa usajili ni sharti la kushiriki katika shughuli za baadaye za ukusanyaji wa data na uchambuzi. Wakati wa usajili, watendaji wa mradi wanapaswa kueleza malengo ya jaribio, taratibu za kuanzisha maeneo ya majaribio, ratiba ya uchunguzi na wajibu wa washiriki katika kipindi chote cha jaribio.</t>
+  </si>
+  <si>
+    <t>Utafiti wa msingi wa kijamii na kiuchumi</t>
+  </si>
+  <si>
+    <t>Utafiti wa msingi wa kijamii na kiuchumi hukusanya taarifa kuhusu sifa za washiriki, muundo wa kaya, shughuli za kilimo, mbinu za usimamizi wa mazao, mifumo ya mbegu, ushiriki katika masoko na upatikanaji wa huduma za kilimo. Madhumuni ya utafiti huu ni kutambua sababu za kijamii na kiuchumi zinazohusiana na usimamizi wa aina za mazao na mapendeleo ya wakulima, pamoja na kusaidia tafsiri ya matokeo ya majaribio katika makundi mbalimbali ya washiriki.</t>
+  </si>
+  <si>
+    <t>Kwa kuwa utafiti wa kijamii na kiuchumi ni mpana zaidi kuliko fomu ya usajili wa washiriki, hauhitaji kufanyika wakati wa ugawaji wa vifurushi vya majaribio. Utafiti unaweza kufanyika wakati wa ziara za ufuatiliaji au wakati mwingine wowote unaofaa katika kipindi cha jaribio. Timu za mradi zinaweza kuutekeleza kwa makundi tofauti ya washiriki katika kipindi chote cha jaribio kulingana na rasilimali zilizopo na vikwazo vya kiutendaji. Ingawa inapendekezwa kwamba washiriki wote washiriki katika utafiti huu, timu za mradi zinaweza kuamua kutumia sampuli inayowakilisha washiriki wote pale ambapo rasilimali ni chache. Kadri inavyowezekana, utafiti huu unapaswa kukamilishwa kabla ya uchambuzi wa mwisho wa data ili kuwezesha kuunganisha taarifa za kijamii na kiuchumi na uchunguzi pamoja na tathmini za washiriki.</t>
+  </si>
+  <si>
+    <t>Vipengele vya dodoso</t>
+  </si>
+  <si>
+    <t>Mfumo wa ukusanyaji wa data wa tricot unajumuisha vipengele mbalimbali vya dodoso vinavyotekelezwa katika kipindi chote cha jaribio. Vipengele hivi hukusanya taarifa zinazokamilishana zinazohitajika kwa usimamizi wa jaribio, ufuatiliaji wa washiriki, uelewa wa mazingira ya jaribio na tathmini ya utendaji wa teknolojia zinazojaribiwa. Ukusanyaji wa data huanza na usajili wa washiriki na ridhaa yenye ufahamu, kisha kufuatiwa na uchunguzi wa hatua mbalimbali za ukuaji wa zao. Kulingana na malengo ya mradi na rasilimali zilizopo, taarifa za ziada za kijamii na kiuchumi zinaweza kukusanywa kutoka kwa washiriki wote au kutoka kwa sampuli inayowakilisha washiriki.</t>
+  </si>
+  <si>
+    <t>Mwisho wa jaribio, washiriki hukamilisha tathmini za mwisho za teknolojia zilizojaribiwa, ikiwa ni pamoja na tathmini za baada ya mavuno. Sehemu zinazofuata zinatoa orodha kamili ya vigezo, maswali na vipindi vya ukusanyaji wa data vinavyohusiana na itifaki hii ya tricot. Dodoso hili linapatikana katika ClimMob kama kiolezo cha mradi kinachoitwa `r templatename`.</t>
+  </si>
+  <si>
+    <t>Rasilimali na SOP nyingine</t>
+  </si>
+  <si>
+    <t>Jedwali lifuatalo linatoa mwongozo wa ziada na SOP zinazoweza kusaidia kupanga, kutekeleza, kuandika na kuchambua majaribio ya tricot.</t>
+  </si>
+  <si>
+    <t>Budget pour un essai tricot</t>
+  </si>
+  <si>
+    <t>Presupuesto para un ensayo tricot</t>
+  </si>
+  <si>
+    <t>Bajeti ya jaribio la tricot</t>
+  </si>
+  <si>
+    <t>Sélection des participants</t>
+  </si>
+  <si>
+    <t>Selección de participantes</t>
+  </si>
+  <si>
+    <t>Uchaguzi wa washiriki</t>
+  </si>
+  <si>
+    <t>Sélection des sites d’essai</t>
+  </si>
+  <si>
+    <t>Selección de sitios de evaluación</t>
+  </si>
+  <si>
+    <t>Uchaguzi wa maeneo ya majaribio</t>
+  </si>
+  <si>
+    <t>Sélection des génotypes</t>
+  </si>
+  <si>
+    <t>Selección de genotipos</t>
+  </si>
+  <si>
+    <t>Uchaguzi wa jenotipu</t>
+  </si>
+  <si>
+    <t>Multiplication des semences</t>
+  </si>
+  <si>
+    <t>Multiplicación de semillas</t>
+  </si>
+  <si>
+    <t>Uzalishaji wa mbegu</t>
+  </si>
+  <si>
+    <t>Documentation des métadonnées de votre essai</t>
+  </si>
+  <si>
+    <t>Documentación de metadatos para su ensayo</t>
+  </si>
+  <si>
+    <t>Kurekodi metadata za jaribio lako</t>
+  </si>
+  <si>
+    <t>Analyse des données</t>
+  </si>
+  <si>
+    <t>Análisis de datos</t>
+  </si>
+  <si>
+    <t>Uchambuzi wa data</t>
+  </si>
+  <si>
+    <t>Estimation du rendement</t>
+  </si>
+  <si>
+    <t>Estimación del rendimiento</t>
+  </si>
+  <si>
+    <t>Ukadiriaji wa mavuno</t>
+  </si>
+  <si>
+    <t>Liste de contrôle pour la mise en œuvre d’un essai tricot</t>
+  </si>
+  <si>
+    <t>Lista de verificación para la implementación de un ensayo tricot</t>
+  </si>
+  <si>
+    <t>Orodha ya ukaguzi ya utekelezaji wa jaribio la tricot</t>
+  </si>
+  <si>
+    <t>Check list for implementing a tricot trial</t>
+  </si>
+  <si>
+    <t>Procédures opérationnelles normalisées pour la mise en œuvre sur le terrain et la collecte de données des essais en exploitation utilisant l’approche tricot</t>
+  </si>
+  <si>
+    <t>Procedimientos operativos estandarizados para la implementación en campo y la recolección de datos de ensayos en finca utilizando el enfoque tricot</t>
+  </si>
+  <si>
+    <t>Taratibu sanifu za utekelezaji wa majaribio shambani na ukusanyaji wa data kwa kutumia mbinu ya tricot</t>
+  </si>
+  <si>
+    <t>Versión</t>
+  </si>
+  <si>
+    <t>Toleo</t>
+  </si>
+  <si>
+    <t>Culture</t>
+  </si>
+  <si>
+    <t>Zao</t>
+  </si>
+  <si>
+    <t>Nom scientifique</t>
+  </si>
+  <si>
+    <t>Nombre científico</t>
+  </si>
+  <si>
+    <t>Jina la kisayansi</t>
+  </si>
+  <si>
+    <t>Auteurs</t>
+  </si>
+  <si>
+    <t>Waandishi</t>
+  </si>
+  <si>
+    <t>Instituciones</t>
+  </si>
+  <si>
+    <t>Taasisi</t>
+  </si>
+  <si>
+    <t>Caractéristiques évaluées</t>
+  </si>
+  <si>
+    <t>Características evaluadas</t>
+  </si>
+  <si>
+    <t>Sifa zinazotathminiwa</t>
+  </si>
+  <si>
+    <t>Moments de collecte des données</t>
+  </si>
+  <si>
+    <t>Momentos de recolección de datos</t>
+  </si>
+  <si>
+    <t>Vipindi vya ukusanyaji wa data</t>
+  </si>
+  <si>
+    <t>Ce document est également disponible en</t>
+  </si>
+  <si>
+    <t>Este documento también está disponible en</t>
+  </si>
+  <si>
+    <t>Hati hii pia inapatikana kwa</t>
+  </si>
+  <si>
+    <t>Nom de la question</t>
+  </si>
+  <si>
+    <t>Nombre de la pregunta</t>
+  </si>
+  <si>
+    <t>Jina la swali</t>
+  </si>
+  <si>
+    <t>Description de la question</t>
+  </si>
+  <si>
+    <t>Descripción de la pregunta</t>
+  </si>
+  <si>
+    <t>Maelezo ya swali</t>
+  </si>
+  <si>
+    <t>Ressource</t>
+  </si>
+  <si>
+    <t>Rasilimali</t>
+  </si>
+  <si>
+    <t>Lien</t>
+  </si>
+  <si>
+    <t>Enlace</t>
+  </si>
+  <si>
+    <t>Kiungo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -533,6 +1007,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -555,18 +1044,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -917,118 +1410,235 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="102" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="272" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>142</v>
+        <v>105</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>72</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>78</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>107</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>80</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>81</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>82</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" t="s">
         <v>91</v>
       </c>
-      <c r="B10" t="s">
-        <v>92</v>
+      <c r="C10" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>85</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>86</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>89</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>88</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -1043,391 +1653,690 @@
   <cols>
     <col min="1" max="1" width="31.33203125" style="3" customWidth="1"/>
     <col min="2" max="2" width="49.83203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="61.5" style="4" customWidth="1"/>
-    <col min="4" max="16384" width="10.83203125" style="3"/>
+    <col min="3" max="3" width="17.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="48.33203125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="45.33203125" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="2" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="238" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="D7" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="221" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="D8" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="356" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="153" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="D22" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="102" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="D33" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="306" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="187" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="153" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="102" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="119" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="68" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="85" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="204" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="170" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="187" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="204" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="153" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="289" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="221" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="119" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>141</v>
+      <c r="D34" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -1442,7 +2351,7 @@
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="34" customWidth="1"/>
+    <col min="3" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -1455,25 +2364,34 @@
       <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>2</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>266</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>34</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -1481,10 +2399,19 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>93</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -1495,7 +2422,16 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>31</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -1506,7 +2442,16 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>37</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -1517,7 +2462,16 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -1528,7 +2482,16 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -1539,7 +2502,16 @@
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>35</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -1550,7 +2522,16 @@
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -1558,10 +2539,19 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>63</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>

--- a/data/base-text-sop.xlsx
+++ b/data/base-text-sop.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-protocols/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D453163F-6D80-3241-B308-7E73BC2F060D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D096186B-320E-6F46-83B6-D0E21941EE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="980" yWindow="600" windowWidth="29740" windowHeight="16700" activeTab="1" xr2:uid="{CCA2DD50-73A2-AB48-A73E-30174A4C4548}"/>
+    <workbookView xWindow="980" yWindow="600" windowWidth="29740" windowHeight="16700" activeTab="2" xr2:uid="{CCA2DD50-73A2-AB48-A73E-30174A4C4548}"/>
   </bookViews>
   <sheets>
     <sheet name="title" sheetId="3" r:id="rId1"/>
@@ -58,9 +58,6 @@
     <t>pt</t>
   </si>
   <si>
-    <t>sw</t>
-  </si>
-  <si>
     <t>fr</t>
   </si>
   <si>
@@ -973,6 +970,9 @@
   </si>
   <si>
     <t>Kiungo</t>
+  </si>
+  <si>
+    <t>swh</t>
   </si>
 </sst>
 </file>
@@ -1403,7 +1403,7 @@
     <col min="2" max="2" width="31.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1411,234 +1411,234 @@
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>2</v>
+      <c r="E1" s="3" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="272" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C2" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>268</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>72</v>
-      </c>
       <c r="D3" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>270</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>272</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" t="s">
         <v>106</v>
       </c>
-      <c r="B5" t="s">
-        <v>107</v>
-      </c>
       <c r="C5" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>275</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>277</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>279</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>282</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>285</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" t="s">
         <v>90</v>
       </c>
-      <c r="B10" t="s">
-        <v>91</v>
-      </c>
       <c r="C10" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>288</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>291</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>294</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C13" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>296</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>299</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -1661,7 +1661,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -1670,673 +1670,673 @@
         <v>1</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F1" s="3" t="s">
-        <v>2</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="D3" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="C4" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="C15" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="356" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="85" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="C21" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="C30" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="306" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="C34" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -2354,9 +2354,9 @@
     <col min="3" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2365,193 +2365,193 @@
         <v>1</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>2</v>
+      <c r="F1" s="3" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>264</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" t="s">
         <v>92</v>
       </c>
-      <c r="C3" t="s">
-        <v>93</v>
-      </c>
       <c r="D3" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>240</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>243</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>246</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>249</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>252</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>255</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>258</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D10" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="5" t="s">
         <v>261</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>262</v>
       </c>
     </row>
   </sheetData>
